--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-548.3%</t>
+          <t>-548.4%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-154.0%</t>
         </is>
       </c>
     </row>
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.86741777417522</v>
+        <v>-3.867877349084349</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479076353983664</v>
+        <v>1.478892524020013</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1758957946766795</v>
+        <v>-0.1763553695858083</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.920862411161492</v>
+        <v>2.920586666216015</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>138.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>549.5%</t>
+          <t>624.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-548.4%</t>
+          <t>-554.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>288.0%</t>
+          <t>-308.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-228.3%</t>
+          <t>-230.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-313.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-154.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-241.6%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-188.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.52216194119703</v>
+        <v>0.4529068635141</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.331078524278007</v>
+        <v>3.303376493204835</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.749136086958278</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.17205182428791</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2850304493472349</v>
+        <v>0.2157753716643049</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.271167012035631</v>
+        <v>3.243464980962459</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.749136086958278</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.206992908785452</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2900680400748214</v>
+        <v>0.2208129623918915</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.271759488512004</v>
+        <v>3.244057457438832</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.804780543224596</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.23895702273058</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.2335984088985246</v>
+        <v>0.1643433312155947</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.227918017665222</v>
+        <v>3.20021598659205</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.748310912048299</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.183821625648539</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1678310188491126</v>
+        <v>0.09857594116618262</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.202628670775927</v>
+        <v>3.174926639702755</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.748310912048299</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.184839234779009</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.154295535072403</v>
+        <v>0.08504045738947302</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.187842509252999</v>
+        <v>3.160140478179827</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.748310912048299</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.175467266766764</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.07252363464465128</v>
+        <v>0.003268556961721347</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.145216475037137</v>
+        <v>3.117514443963965</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.775346485454435</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.181771336765685</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.005314526772773609</v>
+        <v>-0.06394055091015632</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.123098148722088</v>
+        <v>3.095396117648916</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.775346485454435</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.186536653599387</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.009305979567963807</v>
+        <v>-0.05994909811496613</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.122519525959405</v>
+        <v>3.094817494886232</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.779337938249625</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.186756321395742</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4084480439788732</v>
+        <v>-0.4777031216618031</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.953344808045733</v>
+        <v>2.925642776972561</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.361583914702789</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>3.934030798772703</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6300699775369907</v>
+        <v>-0.6993250552199206</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.864562251221408</v>
+        <v>2.836860220148236</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.324057781015419</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>3.911381335159203</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8380740358900679</v>
+        <v>-0.9073291135729978</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.786252772434102</v>
+        <v>2.75855074136093</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.324057781015419</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>3.916273479713128</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.108473998598953</v>
+        <v>-1.177729076281883</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.673174243688536</v>
+        <v>2.645472212615364</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.053657818306534</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.749114958425785</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.447632376187475</v>
+        <v>-1.516887453870405</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.530595191959576</v>
+        <v>2.502893160886404</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.7144994407180121</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.538704231179121</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.775649597914954</v>
+        <v>-1.844904675597884</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.419726593007353</v>
+        <v>2.392024561934181</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.3864822189905329</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.362232187881402</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.268974469450132</v>
+        <v>-2.338229547133063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.23049539480185</v>
+        <v>2.202793363728678</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.2814961047509142</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.307339269746199</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.761359497474229</v>
+        <v>-2.830614575157159</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.034647775635944</v>
+        <v>2.006945744562771</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2108889232731825</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>3.013014644975474</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.146539888404301</v>
+        <v>-3.215794966087232</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.879118158076778</v>
+        <v>1.851416127003606</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2108889232731825</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>3.011557183788337</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.490222661630964</v>
+        <v>-3.559477739313895</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.743414172240729</v>
+        <v>1.715712141167557</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.3187949753004007</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>2.948582676026622</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.847873011869312</v>
+        <v>-3.917128089552243</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.596460090801648</v>
+        <v>1.568758059728475</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.6764453255387488</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.730098524539871</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.157107114865363</v>
+        <v>-4.226362192548294</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.474539376303487</v>
+        <v>1.446837345230315</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.6764453255387488</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.731871451240131</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.588912908015151</v>
+        <v>-4.658167985698081</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.288149946510976</v>
+        <v>1.260447915437804</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.8128628219800158</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.636353840842775</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.915345436882895</v>
+        <v>-4.984600514565825</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.145861709965969</v>
+        <v>1.118159678892797</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8953310724871639</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.575157665540576</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.251008084113347</v>
+        <v>-5.320263161796277</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.010177242729754</v>
+        <v>0.9824752116565816</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8953310724871639</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.573738257196541</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.61463432901366</v>
+        <v>-5.683889406696591</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8712143050038699</v>
+        <v>0.8435122739306977</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.9935527093542897</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.521292835310508</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.979761711652407</v>
+        <v>-6.049016789335337</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7244178669542025</v>
+        <v>0.6967158358810304</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.289863493653302</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.342760879736931</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.388350488833085</v>
+        <v>-6.457605566516015</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5597439000966902</v>
+        <v>0.532041869023518</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>2.096369157443283</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.801332972974179</v>
+        <v>-6.870588050657109</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3897363389117134</v>
+        <v>0.3620343078385413</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>2.091554589914744</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.217724847261176</v>
+        <v>-7.286979924944107</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2211736398057917</v>
+        <v>0.1934716087326196</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>2.089548640523621</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.594401857791021</v>
+        <v>-7.663656935473951</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08076152626253297</v>
+        <v>0.05305949518936082</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>2.0998073311923</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.940276679775829</v>
+        <v>-8.00953175745876</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06148883738569522</v>
+        <v>-0.08919086845886737</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>2.095906896337996</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.253101479020808</v>
+        <v>-8.322356556703738</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1882138370286857</v>
+        <v>-0.2159158681018578</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.698452270833981</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>2.094311816392997</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.549762820831006</v>
+        <v>-8.619017898513937</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3030993978235568</v>
+        <v>-0.3308014288967289</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.767195406567859</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>2.056844910881878</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.983111928941241</v>
+        <v>-9.052367006624172</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4804653456020542</v>
+        <v>-0.5081673766752264</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.767195406567859</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>2.052818606347475</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.366113317683872</v>
+        <v>-9.435368395366803</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6337680024206906</v>
+        <v>-0.6614700334938628</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.767195406567859</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>2.052716505025891</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.74109864385515</v>
+        <v>-9.81035372153808</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7811906169177711</v>
+        <v>-0.8088926479909433</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.142180732739137</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.830296825294554</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10062896635915</v>
+        <v>-10.16988404404208</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.919652442621322</v>
+        <v>-0.9473544736944941</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.142180732739137</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.835647128592604</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42702899502416</v>
+        <v>-10.49628407270709</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.042296434130149</v>
+        <v>-1.069998465203322</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.46858076140415</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.647723131350774</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64617796309836</v>
+        <v>-10.71543304078129</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.126914270738059</v>
+        <v>-1.154616301811231</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.687729729478347</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.519275501128025</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64248703814195</v>
+        <v>-10.71174211582488</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.125437900755495</v>
+        <v>-1.153139931828667</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.687729729478347</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.519275501128025</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84674521347181</v>
+        <v>-10.91600029115475</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.201627973768798</v>
+        <v>-1.22933000484197</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.815368674092336</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.448205331478273</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06478298510299</v>
+        <v>-11.13403806278592</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.284360527936834</v>
+        <v>-1.312062559010006</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.920884364505305</v>
+        <v>-2.990139442188235</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.389378471714928</v>
+        <v>1.34782542510517</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99131315343554</v>
+        <v>-11.06056823111847</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.239600893776433</v>
+        <v>-1.267302924849605</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.847414532837857</v>
+        <v>-2.916669610520787</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.448832072208818</v>
+        <v>1.40727902559906</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16643757082209</v>
+        <v>-11.23569264850502</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.295095439983533</v>
+        <v>-1.322797471056705</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.09179402790733</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.358312642524409</v>
+        <v>1.316759595914651</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40088966483658</v>
+        <v>-11.47014474251951</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.396095442490925</v>
+        <v>-1.423797473564097</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.09179402790733</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.351093477622813</v>
+        <v>1.309540431013055</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.68869350937381</v>
+        <v>-11.75794858705675</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.517889171079796</v>
+        <v>-1.545591202152969</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.310342794761639</v>
+        <v>-3.379597872444569</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.171738980126494</v>
+        <v>1.130185933516736</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91851795653764</v>
+        <v>-11.98777303422057</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.608703160106771</v>
+        <v>-1.636405191179943</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.472990331831799</v>
+        <v>-3.542245409514729</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.075266247722954</v>
+        <v>1.033713201113196</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.1505468762739</v>
+        <v>-12.21980195395683</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.698820999372161</v>
+        <v>-1.726523030445333</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.604258106703152</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.040752358039014</v>
+        <v>0.9991993114292566</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09853136230509</v>
+        <v>-12.16778643998802</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.674024458098234</v>
+        <v>-1.701726489171406</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.604258106703152</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.044742693725415</v>
+        <v>1.003189647115657</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24020320402921</v>
+        <v>-12.30945828171214</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.732168421686624</v>
+        <v>-1.759870452759796</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.604258106703152</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.043267466826673</v>
+        <v>1.001714420216916</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.33910994448848</v>
+        <v>-12.40836502217141</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.756677707705462</v>
+        <v>-1.784379738778635</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.633909769479498</v>
+        <v>-3.703164847162428</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9989768327159809</v>
+        <v>0.9574237861062227</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.13995783725139</v>
+        <v>-12.20921291493432</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.690067998457306</v>
+        <v>-1.717770029530478</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.468587243529684</v>
+        <v>-3.537842321212615</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.085119214639186</v>
+        <v>1.043566168029427</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.91411268453198</v>
+        <v>-11.9833677622149</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.590150864333333</v>
+        <v>-1.617852895406504</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.495915645625451</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.119854293027692</v>
+        <v>1.078301246417934</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.62783787220928</v>
+        <v>-11.69709294989221</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.474501794848196</v>
+        <v>-1.502203825921367</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.495915645625451</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.120993437583751</v>
+        <v>1.079440390973993</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68073316025357</v>
+        <v>-11.7499882379365</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.493026135903803</v>
+        <v>-1.520728166976975</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.490960299537005</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.126600419398927</v>
+        <v>1.085047372789169</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39682442932482</v>
+        <v>-11.46607950700775</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.373728939293667</v>
+        <v>-1.401430970366838</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.490960299537005</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.132334123637563</v>
+        <v>1.090781077027805</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.14983717913187</v>
+        <v>-11.2190922568148</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.284671301610351</v>
+        <v>-1.312373332683523</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.243973049344053</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.270789211359469</v>
+        <v>1.229236164749711</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.8860003119278</v>
+        <v>-10.95525538961073</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.189020036041631</v>
+        <v>-1.216722067114803</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.243973049344053</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.260905730046562</v>
+        <v>1.219352683436804</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6187585110594</v>
+        <v>-10.68801358874233</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.083957876193646</v>
+        <v>-1.111659907266817</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.243973049344053</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.259071169547188</v>
+        <v>1.21751812293743</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.34294934765891</v>
+        <v>-10.41220442534184</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.973934525806913</v>
+        <v>-1.001636556880084</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.085698663382389</v>
+        <v>-3.154953741065319</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.312182439540967</v>
+        <v>1.270629392931209</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.31899580668296</v>
+        <v>-10.38825088436588</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.963684603271036</v>
+        <v>-0.9913866343442073</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.061745122406431</v>
+        <v>-3.131000200089362</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.327223070272036</v>
+        <v>1.285670023662277</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.05493586836016</v>
+        <v>-10.12419094604309</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8713209441036689</v>
+        <v>-0.899022975176841</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.866940261766566</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.472398717103961</v>
+        <v>1.430845670494203</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.347856244855322</v>
+        <v>-9.417111322538251</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5912761283620354</v>
+        <v>-0.6189781594352066</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.866940261766566</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.46961168344366</v>
+        <v>1.428058636833902</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.307671946489132</v>
+        <v>-9.37692702417206</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5748587851277178</v>
+        <v>-0.6025608162008891</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.757500885717445</v>
+        <v>-2.826755963400375</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.494065886351216</v>
+        <v>1.452512839741458</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.227602150951327</v>
+        <v>-9.296857228634256</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5434640456918389</v>
+        <v>-0.5711660767650102</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.677431090179641</v>
+        <v>-2.746686167862571</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.541474584894655</v>
+        <v>1.499921538284897</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.994120928721728</v>
+        <v>-9.063376006404656</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4421471279621469</v>
+        <v>-0.4698491590353182</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.443949867950042</v>
+        <v>-2.513204945632972</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.689487747070267</v>
+        <v>1.647934700460508</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.814412398577854</v>
+        <v>-8.883667476260783</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3731559262175566</v>
+        <v>-0.4008579572907278</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.386778363787346</v>
+        <v>-2.456033441470276</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.720898439254925</v>
+        <v>1.679345392645167</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.682136924946967</v>
+        <v>-8.751392002629895</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3248782500181746</v>
+        <v>-0.3525802810913459</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.25450289015646</v>
+        <v>-2.32375796783939</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.795631210180484</v>
+        <v>1.754078163570726</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.491537250273813</v>
+        <v>-8.560792327956742</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2458233194612767</v>
+        <v>-0.2735253505344479</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.133158293166237</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.912806075672012</v>
+        <v>1.871253029062254</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.242537451590232</v>
+        <v>-8.311792529273161</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1333170587641854</v>
+        <v>-0.1610190898373567</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.133158293166237</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.925712416895671</v>
+        <v>1.884159370285913</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.348127441363337</v>
+        <v>-8.417382519046265</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3035289842726456</v>
+        <v>-0.3312310153458173</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.238748282939342</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.73438249343259</v>
+        <v>1.692829446822832</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.366862343481934</v>
+        <v>-8.436117421164862</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2624786032429984</v>
+        <v>-0.2901806343161697</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.238748282939342</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.782926835309676</v>
+        <v>1.741373788699918</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.090124168811121</v>
+        <v>-8.15937924649405</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1484043213886785</v>
+        <v>-0.1761063524618498</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.987676544146486</v>
+        <v>-2.056931621829416</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.895395843961626</v>
+        <v>1.853842797351868</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.963231762376051</v>
+        <v>-8.032486840058979</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1063613450681284</v>
+        <v>-0.1340633761413002</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.930039215394346</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.96281730156919</v>
+        <v>1.921264254959432</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.91968335560536</v>
+        <v>-7.988938433288289</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09590259445494542</v>
+        <v>-0.1236046255281171</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.930039215394346</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.955856689474097</v>
+        <v>1.914303642864339</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.677534962151502</v>
+        <v>-7.746790039834431</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01541911730774093</v>
+        <v>-0.01228291376543078</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.930039215394346</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.97031904385524</v>
+        <v>1.928765997245482</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.614305590383154</v>
+        <v>-7.683560668066082</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03524298647427537</v>
+        <v>0.007540955401103666</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.930039215394346</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.964851164314435</v>
+        <v>1.923298117704677</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.427817898006148</v>
+        <v>-7.497072975689076</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1073361574356544</v>
+        <v>0.07963412636248313</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.67429644533441</v>
+        <v>-1.74355152301734</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.074241873751216</v>
+        <v>2.032688827141457</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.406668699102704</v>
+        <v>-7.475923776785633</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1234968152343576</v>
+        <v>0.09579478416118592</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.722402324113897</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.094632371330607</v>
+        <v>2.053079324720849</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.16290325711926</v>
+        <v>-7.232158334802189</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2167837003747857</v>
+        <v>0.1890816693016144</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.722402324113897</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.090413079677658</v>
+        <v>2.0488600330679</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.898875189926001</v>
+        <v>-6.968130267608929</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3245192411721058</v>
+        <v>0.2968172100989341</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.520536925297943</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.213656632887246</v>
+        <v>2.172103586277488</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.649024795976926</v>
+        <v>-6.718279873659855</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4172014737354375</v>
+        <v>0.3894994426622662</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.520536925297943</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.206398707870948</v>
+        <v>2.16484566126119</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.345457306972947</v>
+        <v>-6.414712384655876</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5422275928576781</v>
+        <v>0.5145255617845064</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.520536925297943</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.209997831391597</v>
+        <v>2.168444784781839</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.271977398120933</v>
+        <v>-6.341232475803862</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5849470624530371</v>
+        <v>0.5572450313798658</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.377801938762998</v>
+        <v>-1.447057016445929</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.267413282757359</v>
+        <v>2.225860236147601</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.04694439845211</v>
+        <v>-6.116199476135039</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6739807399368631</v>
+        <v>0.6462787088636919</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.152768939094175</v>
+        <v>-1.222024016777106</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.40145356017495</v>
+        <v>2.359900513565192</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.832310020815703</v>
+        <v>-5.901565098498632</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7645292920457436</v>
+        <v>0.7368272609725719</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.007389639140699</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.534928987811111</v>
+        <v>2.493375941201353</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.565709663841352</v>
+        <v>-5.63496474152428</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8523636936192798</v>
+        <v>0.8246616625461085</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.007389639140699</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.516123246594907</v>
+        <v>2.474570199985149</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.325279167036491</v>
+        <v>-5.39453424471942</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9502789689661011</v>
+        <v>0.9225769378929298</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.7669591423358386</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.6621246213027</v>
+        <v>2.620571574692942</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.082488359387046</v>
+        <v>-5.151743437069975</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.0513246058607</v>
+        <v>1.023622574787528</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.7669591423358386</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.666053935137521</v>
+        <v>2.624500888527762</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.842883267779957</v>
+        <v>-4.912138345462886</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.147845226420875</v>
+        <v>1.120143195347704</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.6999111946673441</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.706961287655957</v>
+        <v>2.665408241046199</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.600227679356793</v>
+        <v>-4.669482757039722</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241905533010134</v>
+        <v>1.214203501936963</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.6999111946673441</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.703959358875951</v>
+        <v>2.662406312266193</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.380206881319783</v>
+        <v>-4.449461959002711</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.331492889235553</v>
+        <v>1.303790858162381</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.5586913495993638</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.790270302927353</v>
+        <v>2.748717256317595</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.180958251414974</v>
+        <v>-4.250213329097902</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.4270865239993</v>
+        <v>1.399384492926128</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.5586913495993638</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.806164485729176</v>
+        <v>2.764611439119418</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.021443147895604</v>
+        <v>-4.090698225578532</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.492038409847349</v>
+        <v>1.464336378774178</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3299211683970635</v>
+        <v>-0.3991762460799939</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.9030193922811</v>
+        <v>2.861466345671342</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.876771002795866</v>
+        <v>-3.946026080478795</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.559995370448684</v>
+        <v>1.532293339375513</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1852490232973261</v>
+        <v>-0.2545041009802565</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.999910781902383</v>
+        <v>2.958357735292624</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.490356567803609</v>
+        <v>3.563291348712937</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.867877349084349</v>
+        <v>-3.92825662154784</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.478892524020013</v>
+        <v>1.454740815034616</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1763553695858083</v>
+        <v>-0.2367346420493009</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.920586666216015</v>
+        <v>2.884359102737919</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>119.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.6%</t>
+          <t>138.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.7%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>624.1%</t>
+          <t>553.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-554.4%</t>
+          <t>-536.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-308.7%</t>
+          <t>309.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.7%</t>
+          <t>-223.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-313.5%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-152.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-240.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-188.5%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-153.4%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4529068635141</v>
+        <v>0.52216194119703</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.303376493204835</v>
+        <v>3.331078524278007</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.749136086958278</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.17205182428791</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2157753716643049</v>
+        <v>0.2850304493472349</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.243464980962459</v>
+        <v>3.271167012035631</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.749136086958278</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.206992908785452</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2208129623918915</v>
+        <v>0.2900680400748214</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.244057457438832</v>
+        <v>3.271759488512004</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.804780543224596</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.23895702273058</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1643433312155947</v>
+        <v>0.2335984088985246</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.20021598659205</v>
+        <v>3.227918017665222</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.748310912048299</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.183821625648539</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.09857594116618262</v>
+        <v>0.1678310188491126</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.174926639702755</v>
+        <v>3.202628670775927</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.748310912048299</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.184839234779009</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.08504045738947302</v>
+        <v>0.154295535072403</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.160140478179827</v>
+        <v>3.187842509252999</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.748310912048299</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.175467266766764</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.003268556961721347</v>
+        <v>0.07252363464465128</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.117514443963965</v>
+        <v>3.145216475037137</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.775346485454435</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.181771336765685</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.06394055091015632</v>
+        <v>0.005314526772773609</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.095396117648916</v>
+        <v>3.123098148722088</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.775346485454435</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.186536653599387</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.05994909811496613</v>
+        <v>0.009305979567963807</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.094817494886232</v>
+        <v>3.122519525959405</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.779337938249625</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.186756321395742</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4777031216618031</v>
+        <v>-0.4084480439788732</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.925642776972561</v>
+        <v>2.953344808045733</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.361583914702789</v>
+        <v>1.430838992385719</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.934030798772703</v>
+        <v>3.975583845382461</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6993250552199206</v>
+        <v>-0.6300699775369907</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.836860220148236</v>
+        <v>2.864562251221408</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.324057781015419</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.911381335159203</v>
+        <v>3.952934381768961</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9073291135729978</v>
+        <v>-0.8380740358900679</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.75855074136093</v>
+        <v>2.786252772434102</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.324057781015419</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.916273479713128</v>
+        <v>3.957826526322886</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.177729076281883</v>
+        <v>-1.108473998598953</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.645472212615364</v>
+        <v>2.673174243688536</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.053657818306534</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.749114958425785</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.516887453870405</v>
+        <v>-1.447632376187475</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.502893160886404</v>
+        <v>2.530595191959576</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7144994407180121</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.538704231179121</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.844904675597884</v>
+        <v>-1.775649597914954</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.392024561934181</v>
+        <v>2.419726593007353</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3864822189905329</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.362232187881402</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.338229547133063</v>
+        <v>-2.268974469450132</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.202793363728678</v>
+        <v>2.23049539480185</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2814961047509142</v>
+        <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.307339269746199</v>
+        <v>3.348892316355957</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.830614575157159</v>
+        <v>-2.761359497474229</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.006945744562771</v>
+        <v>2.034647775635944</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2108889232731825</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.013014644975474</v>
+        <v>3.054567691585231</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.215794966087232</v>
+        <v>-3.146539888404301</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.851416127003606</v>
+        <v>1.879118158076778</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2108889232731825</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.011557183788337</v>
+        <v>3.053110230398095</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.559477739313895</v>
+        <v>-3.490222661630964</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.715712141167557</v>
+        <v>1.743414172240729</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3187949753004007</v>
+        <v>-0.2495398976174708</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.948582676026622</v>
+        <v>2.99013572263638</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.917128089552243</v>
+        <v>-3.847873011869312</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.568758059728475</v>
+        <v>1.596460090801648</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6764453255387488</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.730098524539871</v>
+        <v>2.771651571149629</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.226362192548294</v>
+        <v>-4.157107114865363</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.446837345230315</v>
+        <v>1.474539376303487</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6764453255387488</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.731871451240131</v>
+        <v>2.773424497849888</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.658167985698081</v>
+        <v>-4.588912908015151</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.260447915437804</v>
+        <v>1.288149946510976</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8128628219800158</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.636353840842775</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.984600514565825</v>
+        <v>-4.915345436882895</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.118159678892797</v>
+        <v>1.145861709965969</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8953310724871639</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.575157665540576</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.320263161796277</v>
+        <v>-5.251008084113347</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9824752116565816</v>
+        <v>1.010177242729754</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8953310724871639</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.573738257196541</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.683889406696591</v>
+        <v>-5.61463432901366</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8435122739306977</v>
+        <v>0.8712143050038699</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9935527093542897</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.521292835310508</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.049016789335337</v>
+        <v>-5.979761711652407</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6967158358810304</v>
+        <v>0.7244178669542025</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.289863493653302</v>
+        <v>-1.220608415970372</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.342760879736931</v>
+        <v>2.38431392634669</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.457605566516015</v>
+        <v>-6.388350488833085</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.532041869023518</v>
+        <v>0.5597439000966902</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.096369157443283</v>
+        <v>2.137922204053042</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.870588050657109</v>
+        <v>-6.801332972974179</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3620343078385413</v>
+        <v>0.3897363389117134</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.091554589914744</v>
+        <v>2.133107636524502</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.286979924944107</v>
+        <v>-7.217724847261176</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1934716087326196</v>
+        <v>0.2211736398057917</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.089548640523621</v>
+        <v>2.13110168713338</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.663656935473951</v>
+        <v>-7.594401857791021</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05305949518936082</v>
+        <v>0.08076152626253297</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.0998073311923</v>
+        <v>2.141360377802059</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.00953175745876</v>
+        <v>-7.940276679775829</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08919086845886737</v>
+        <v>-0.06148883738569522</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.095906896337996</v>
+        <v>2.137459942947754</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.322356556703738</v>
+        <v>-8.253101479020808</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2159158681018578</v>
+        <v>-0.1882138370286857</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.698452270833981</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.094311816392997</v>
+        <v>2.135864863002755</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.619017898513937</v>
+        <v>-8.549762820831006</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3308014288967289</v>
+        <v>-0.3030993978235568</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.767195406567859</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.056844910881878</v>
+        <v>2.098397957491636</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.052367006624172</v>
+        <v>-8.983111928941241</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5081673766752264</v>
+        <v>-0.4804653456020542</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.767195406567859</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.052818606347475</v>
+        <v>2.094371652957232</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.435368395366803</v>
+        <v>-9.366113317683872</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6614700334938628</v>
+        <v>-0.6337680024206906</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.767195406567859</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.052716505025891</v>
+        <v>2.094269551635648</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.81035372153808</v>
+        <v>-9.74109864385515</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8088926479909433</v>
+        <v>-0.7811906169177711</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.142180732739137</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.830296825294554</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.16988404404208</v>
+        <v>-10.10062896635915</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9473544736944941</v>
+        <v>-0.919652442621322</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.142180732739137</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.835647128592604</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.49628407270709</v>
+        <v>-10.42702899502416</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.069998465203322</v>
+        <v>-1.042296434130149</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.46858076140415</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.647723131350774</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.71543304078129</v>
+        <v>-10.64617796309836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.154616301811231</v>
+        <v>-1.126914270738059</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.687729729478347</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.519275501128025</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.71174211582488</v>
+        <v>-10.64248703814195</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.153139931828667</v>
+        <v>-1.125437900755495</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.687729729478347</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.519275501128025</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.91600029115475</v>
+        <v>-10.84674521347181</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.22933000484197</v>
+        <v>-1.201627973768798</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.815368674092336</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.448205331478273</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.13403806278592</v>
+        <v>-11.06478298510299</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.312062559010006</v>
+        <v>-1.284360527936834</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.990139442188235</v>
+        <v>-2.920884364505305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.34782542510517</v>
+        <v>1.389378471714928</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.06056823111847</v>
+        <v>-10.99131315343554</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.267302924849605</v>
+        <v>-1.239600893776433</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.916669610520787</v>
+        <v>-2.847414532837857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.40727902559906</v>
+        <v>1.448832072208818</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.23569264850502</v>
+        <v>-11.16643757082209</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.322797471056705</v>
+        <v>-1.295095439983533</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.09179402790733</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.316759595914651</v>
+        <v>1.358312642524409</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.47014474251951</v>
+        <v>-11.40088966483658</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.423797473564097</v>
+        <v>-1.396095442490925</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.09179402790733</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.309540431013055</v>
+        <v>1.351093477622813</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.75794858705675</v>
+        <v>-11.68869350937381</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.545591202152969</v>
+        <v>-1.517889171079796</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.379597872444569</v>
+        <v>-3.310342794761639</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.130185933516736</v>
+        <v>1.171738980126494</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.98777303422057</v>
+        <v>-11.91851795653764</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.636405191179943</v>
+        <v>-1.608703160106771</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.542245409514729</v>
+        <v>-3.472990331831799</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.033713201113196</v>
+        <v>1.075266247722954</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.21980195395683</v>
+        <v>-12.1505468762739</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.726523030445333</v>
+        <v>-1.698820999372161</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.604258106703152</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9991993114292566</v>
+        <v>1.040752358039014</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.16778643998802</v>
+        <v>-12.09853136230509</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.701726489171406</v>
+        <v>-1.674024458098234</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.604258106703152</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.003189647115657</v>
+        <v>1.044742693725415</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.30945828171214</v>
+        <v>-12.24020320402921</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.759870452759796</v>
+        <v>-1.732168421686624</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.604258106703152</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.001714420216916</v>
+        <v>1.043267466826673</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.40836502217141</v>
+        <v>-12.33910994448848</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.784379738778635</v>
+        <v>-1.756677707705462</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.703164847162428</v>
+        <v>-3.633909769479498</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9574237861062227</v>
+        <v>0.9989768327159809</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.20921291493432</v>
+        <v>-12.13995783725139</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.717770029530478</v>
+        <v>-1.690067998457306</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.537842321212615</v>
+        <v>-3.468587243529684</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.043566168029427</v>
+        <v>1.085119214639186</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.9833677622149</v>
+        <v>-11.91411268453198</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.617852895406504</v>
+        <v>-1.590150864333333</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.495915645625451</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.078301246417934</v>
+        <v>1.119854293027692</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.69709294989221</v>
+        <v>-11.62783787220928</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.502203825921367</v>
+        <v>-1.474501794848196</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.495915645625451</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.079440390973993</v>
+        <v>1.120993437583751</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.7499882379365</v>
+        <v>-11.68073316025357</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.520728166976975</v>
+        <v>-1.493026135903803</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.490960299537005</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.085047372789169</v>
+        <v>1.126600419398927</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.46607950700775</v>
+        <v>-11.39682442932482</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.401430970366838</v>
+        <v>-1.373728939293667</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.490960299537005</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.090781077027805</v>
+        <v>1.132334123637563</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.2190922568148</v>
+        <v>-11.14983717913187</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.312373332683523</v>
+        <v>-1.284671301610351</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.243973049344053</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.229236164749711</v>
+        <v>1.270789211359469</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.95525538961073</v>
+        <v>-10.8860003119278</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.216722067114803</v>
+        <v>-1.189020036041631</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.243973049344053</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.219352683436804</v>
+        <v>1.260905730046562</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.68801358874233</v>
+        <v>-10.6187585110594</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.111659907266817</v>
+        <v>-1.083957876193646</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.243973049344053</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.21751812293743</v>
+        <v>1.259071169547188</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.41220442534184</v>
+        <v>-10.34294934765891</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.001636556880084</v>
+        <v>-0.973934525806913</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.154953741065319</v>
+        <v>-3.085698663382389</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.270629392931209</v>
+        <v>1.312182439540967</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.38825088436588</v>
+        <v>-10.31899580668296</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9913866343442073</v>
+        <v>-0.963684603271036</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.131000200089362</v>
+        <v>-3.061745122406431</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.285670023662277</v>
+        <v>1.327223070272036</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.12419094604309</v>
+        <v>-10.05493586836016</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.899022975176841</v>
+        <v>-0.8713209441036689</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.866940261766566</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.430845670494203</v>
+        <v>1.472398717103961</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.417111322538251</v>
+        <v>-9.347856244855322</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6189781594352066</v>
+        <v>-0.5912761283620354</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.866940261766566</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.428058636833902</v>
+        <v>1.46961168344366</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.37692702417206</v>
+        <v>-9.307671946489132</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6025608162008891</v>
+        <v>-0.5748587851277178</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.826755963400375</v>
+        <v>-2.757500885717445</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.452512839741458</v>
+        <v>1.494065886351216</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.296857228634256</v>
+        <v>-9.227602150951327</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5711660767650102</v>
+        <v>-0.5434640456918389</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.746686167862571</v>
+        <v>-2.677431090179641</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.499921538284897</v>
+        <v>1.541474584894655</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.063376006404656</v>
+        <v>-8.994120928721728</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4698491590353182</v>
+        <v>-0.4421471279621469</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.513204945632972</v>
+        <v>-2.443949867950042</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.647934700460508</v>
+        <v>1.689487747070267</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.883667476260783</v>
+        <v>-8.814412398577854</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4008579572907278</v>
+        <v>-0.3731559262175566</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.456033441470276</v>
+        <v>-2.386778363787346</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.679345392645167</v>
+        <v>1.720898439254925</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.751392002629895</v>
+        <v>-8.682136924946967</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3525802810913459</v>
+        <v>-0.3248782500181746</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.32375796783939</v>
+        <v>-2.25450289015646</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.754078163570726</v>
+        <v>1.795631210180484</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.560792327956742</v>
+        <v>-8.491537250273813</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2735253505344479</v>
+        <v>-0.2458233194612767</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.133158293166237</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.871253029062254</v>
+        <v>1.912806075672012</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.311792529273161</v>
+        <v>-8.242537451590232</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1610190898373567</v>
+        <v>-0.1333170587641854</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.133158293166237</v>
+        <v>-2.063903215483307</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.884159370285913</v>
+        <v>1.925712416895671</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.417382519046265</v>
+        <v>-8.348127441363337</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3312310153458173</v>
+        <v>-0.3035289842726456</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.238748282939342</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.692829446822832</v>
+        <v>1.73438249343259</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.436117421164862</v>
+        <v>-8.366862343481934</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2901806343161697</v>
+        <v>-0.2624786032429984</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.238748282939342</v>
+        <v>-2.169493205256412</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.741373788699918</v>
+        <v>1.782926835309676</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.15937924649405</v>
+        <v>-8.090124168811121</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1761063524618498</v>
+        <v>-0.1484043213886785</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.056931621829416</v>
+        <v>-1.987676544146486</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.853842797351868</v>
+        <v>1.895395843961626</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.032486840058979</v>
+        <v>-7.963231762376051</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1340633761413002</v>
+        <v>-0.1063613450681284</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.930039215394346</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.921264254959432</v>
+        <v>1.96281730156919</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.988938433288289</v>
+        <v>-7.91968335560536</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1236046255281171</v>
+        <v>-0.09590259445494542</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.930039215394346</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.914303642864339</v>
+        <v>1.955856689474097</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.746790039834431</v>
+        <v>-7.677534962151502</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01228291376543078</v>
+        <v>0.01541911730774093</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.930039215394346</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.928765997245482</v>
+        <v>1.97031904385524</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.683560668066082</v>
+        <v>-7.507695563948653</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.007540955401103666</v>
+        <v>0.07788699704807556</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.930039215394346</v>
+        <v>-1.860784137711416</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.923298117704677</v>
+        <v>1.964851164314435</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.497072975689076</v>
+        <v>-7.321207871571647</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.07963412636248313</v>
+        <v>0.1499801680094546</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.74355152301734</v>
+        <v>-1.67429644533441</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.032688827141457</v>
+        <v>2.074241873751216</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.475923776785633</v>
+        <v>-7.300058672668204</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.09579478416118592</v>
+        <v>0.1661408258081578</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.722402324113897</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.053079324720849</v>
+        <v>2.094632371330607</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.232158334802189</v>
+        <v>-7.056293230684759</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1890816693016144</v>
+        <v>0.2594277109485863</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.722402324113897</v>
+        <v>-1.653147246430966</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.0488600330679</v>
+        <v>2.090413079677658</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.968130267608929</v>
+        <v>-6.7922651634915</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2968172100989341</v>
+        <v>0.367163251745906</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.520536925297943</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172103586277488</v>
+        <v>2.213656632887246</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.718279873659855</v>
+        <v>-6.542414769542425</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3894994426622662</v>
+        <v>0.4598454843092381</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.520536925297943</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.16484566126119</v>
+        <v>2.206398707870948</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.414712384655876</v>
+        <v>-6.238847280538447</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5145255617845064</v>
+        <v>0.5848716034314783</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.520536925297943</v>
+        <v>-1.451281847615013</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.168444784781839</v>
+        <v>2.209997831391597</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.341232475803862</v>
+        <v>-6.165367371686433</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5572450313798658</v>
+        <v>0.6275910730268373</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.447057016445929</v>
+        <v>-1.377801938762998</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.225860236147601</v>
+        <v>2.267413282757359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.116199476135039</v>
+        <v>-5.94033437201761</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6462787088636919</v>
+        <v>0.7166247505106638</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.222024016777106</v>
+        <v>-1.152768939094175</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.359900513565192</v>
+        <v>2.40145356017495</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.901565098498632</v>
+        <v>-5.725699994381203</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7368272609725719</v>
+        <v>0.8071733026195438</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.007389639140699</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.493375941201353</v>
+        <v>2.534928987811111</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.63496474152428</v>
+        <v>-5.459099637406851</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8246616625461085</v>
+        <v>0.89500770419308</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.007389639140699</v>
+        <v>-0.9381345614577685</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.474570199985149</v>
+        <v>2.516123246594907</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.39453424471942</v>
+        <v>-5.218669140601991</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9225769378929298</v>
+        <v>0.9929229795399017</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7669591423358386</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.620571574692942</v>
+        <v>2.6621246213027</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.151743437069975</v>
+        <v>-4.975878332952545</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.023622574787528</v>
+        <v>1.0939686164345</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7669591423358386</v>
+        <v>-0.6977040646529082</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.624500888527762</v>
+        <v>2.666053935137521</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.912138345462886</v>
+        <v>-4.736273241345456</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.120143195347704</v>
+        <v>1.190489236994676</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6999111946673441</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.665408241046199</v>
+        <v>2.706961287655957</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.669482757039722</v>
+        <v>-4.493617652922293</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.214203501936963</v>
+        <v>1.284549543583934</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6999111946673441</v>
+        <v>-0.6306561169844137</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.662406312266193</v>
+        <v>2.703959358875951</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.449461959002711</v>
+        <v>-4.273596854885282</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.303790858162381</v>
+        <v>1.374136899809353</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5586913495993638</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.748717256317595</v>
+        <v>2.790270302927353</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.250213329097902</v>
+        <v>-4.074348224980473</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399384492926128</v>
+        <v>1.4697305345731</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5586913495993638</v>
+        <v>-0.4894362719164335</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.764611439119418</v>
+        <v>2.806164485729176</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.090698225578532</v>
+        <v>-3.914833121461103</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.464336378774178</v>
+        <v>1.53468242042115</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3991762460799939</v>
+        <v>-0.3299211683970635</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.861466345671342</v>
+        <v>2.9030193922811</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.946026080478795</v>
+        <v>-3.770160976361366</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.532293339375513</v>
+        <v>1.602639381022484</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2545041009802565</v>
+        <v>-0.1852490232973261</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.958357735292624</v>
+        <v>2.999910781902383</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.563291348712937</v>
+        <v>3.763576486342096</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.92825662154784</v>
+        <v>-3.75239151743041</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.454740815034616</v>
+        <v>1.525086856681588</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2367346420493009</v>
+        <v>-0.1674795643663706</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.884359102737919</v>
+        <v>2.925912149347678</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.0%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>553.9%</t>
+          <t>662.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-536.8%</t>
+          <t>-558.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>309.4%</t>
+          <t>-195.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-223.7%</t>
+          <t>-232.4%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-315.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-154.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.7%</t>
+          <t>-251.9%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-189.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-153.4%</t>
+          <t>-147.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1933"/>
+  <dimension ref="A1:G1934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.52216194119703</v>
+        <v>0.4367914390125668</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.331078524278007</v>
+        <v>3.296930323404222</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.733020662456745</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.16238256958699</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2850304493472349</v>
+        <v>0.1996599471627717</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.271167012035631</v>
+        <v>3.237018811161846</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.733020662456745</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.197323654084531</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2900680400748214</v>
+        <v>0.2046975378903583</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.271759488512004</v>
+        <v>3.237611287638218</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.788665118723062</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.229287768029661</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.2335984088985246</v>
+        <v>0.1482279067140615</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.227918017665222</v>
+        <v>3.193769816791437</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.732195487546766</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.174152370947619</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1678310188491126</v>
+        <v>0.08246051666464943</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.202628670775927</v>
+        <v>3.168480469902142</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.732195487546766</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.175169980078089</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.154295535072403</v>
+        <v>0.06892503288793983</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.187842509252999</v>
+        <v>3.153694308379214</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.732195487546766</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.165798012065845</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.07252363464465128</v>
+        <v>-0.01284686753981185</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.145216475037137</v>
+        <v>3.111068274163352</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.759231060952902</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.172102082064765</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.005314526772773609</v>
+        <v>-0.08005597541168952</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.123098148722088</v>
+        <v>3.088949947848303</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.759231060952902</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.176867398898468</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.009305979567963807</v>
+        <v>-0.07606452261649932</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.122519525959405</v>
+        <v>3.088371325085619</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.763222513748092</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.177087066694822</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4084480439788732</v>
+        <v>-0.4938185461633363</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.953344808045733</v>
+        <v>2.919196607171948</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.345468490201255</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>3.924361544071783</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6300699775369907</v>
+        <v>-0.7154404797214537</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.864562251221408</v>
+        <v>2.830414050347622</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.307942356513886</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>3.901712080458283</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8380740358900679</v>
+        <v>-0.923444538074531</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.786252772434102</v>
+        <v>2.752104571560317</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.307942356513886</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>3.906604225012209</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.108473998598953</v>
+        <v>-1.193844500783416</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.673174243688536</v>
+        <v>2.639026042814751</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.037542393805001</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.739445703724865</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.447632376187475</v>
+        <v>-1.533002878371938</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.530595191959576</v>
+        <v>2.496446991085791</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.6983840162164789</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.529034976478201</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.775649597914954</v>
+        <v>-1.861020100099417</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.419726593007353</v>
+        <v>2.385578392133568</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.3703667944889998</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.352562933180482</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.268974469450132</v>
+        <v>-2.354344971634595</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.23049539480185</v>
+        <v>2.196347193928065</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.2653806802493811</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.297670015045279</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.761359497474229</v>
+        <v>-2.846729999658692</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.034647775635944</v>
+        <v>2.000499574762158</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2270043477747157</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>3.003345390274553</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.146539888404301</v>
+        <v>-3.231910390588765</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.879118158076778</v>
+        <v>1.844969957202993</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2270043477747157</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>3.001887929087417</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.490222661630964</v>
+        <v>-3.575593163815427</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.743414172240729</v>
+        <v>1.709265971366944</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.3349103998019339</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>2.938913421325702</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.847873011869312</v>
+        <v>-3.933243514053775</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.596460090801648</v>
+        <v>1.562311889927862</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.6925607500402819</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.720429269838951</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.157107114865363</v>
+        <v>-4.242477617049826</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.474539376303487</v>
+        <v>1.440391175429702</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.6925607500402819</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.72220219653921</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.588912908015151</v>
+        <v>-4.674283410199613</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.288149946510976</v>
+        <v>1.254001745637191</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.8289782464815489</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.626684586141855</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.915345436882895</v>
+        <v>-5.000715939067357</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.145861709965969</v>
+        <v>1.111713509092184</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.9114464969886971</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.565488410839657</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.251008084113347</v>
+        <v>-5.336378586297809</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.010177242729754</v>
+        <v>0.9760290418559685</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.9114464969886971</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.564069002495622</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.61463432901366</v>
+        <v>-5.700004831198123</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8712143050038699</v>
+        <v>0.8370661041300846</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-1.009668133855823</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.511623580609588</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.979761711652407</v>
+        <v>-6.065132213836869</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7244178669542025</v>
+        <v>0.6902696660804173</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.305978918154835</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.333091625036012</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.388350488833085</v>
+        <v>-6.473720991017548</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5597439000966902</v>
+        <v>0.5255956992229045</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>2.086699902742364</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.801332972974179</v>
+        <v>-6.886703475158642</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3897363389117134</v>
+        <v>0.3555881380379278</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>2.081885335213824</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.217724847261176</v>
+        <v>-7.303095349445639</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2211736398057917</v>
+        <v>0.1870254389320061</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>2.079879385822702</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.594401857791021</v>
+        <v>-7.679772359975484</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08076152626253297</v>
+        <v>0.0466133253887473</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>2.090138076491381</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.940276679775829</v>
+        <v>-8.025647181960291</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06148883738569522</v>
+        <v>-0.09563703825948089</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>2.086237641637076</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.253101479020808</v>
+        <v>-8.33847198120527</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1882138370286857</v>
+        <v>-0.2223620379024713</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.714567695335514</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>2.084642561692077</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.549762820831006</v>
+        <v>-8.635133323015468</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3030993978235568</v>
+        <v>-0.3372475986973424</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.783310831069392</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>2.047175656180958</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.983111928941241</v>
+        <v>-9.068482431125704</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4804653456020542</v>
+        <v>-0.5146135464758395</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.783310831069392</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>2.043149351646555</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.366113317683872</v>
+        <v>-9.451483819868335</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6337680024206906</v>
+        <v>-0.6679162032944763</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.783310831069392</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>2.043047250324971</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.74109864385515</v>
+        <v>-9.826469146039612</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7811906169177711</v>
+        <v>-0.8153388177915568</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.15829615724067</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.820627570593634</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10062896635915</v>
+        <v>-10.18599946854361</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.919652442621322</v>
+        <v>-0.9538006434951072</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.15829615724067</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.825977873891685</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42702899502416</v>
+        <v>-10.51239949720863</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.042296434130149</v>
+        <v>-1.076444635003935</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.484696185905683</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.638053876649854</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64617796309836</v>
+        <v>-10.73154846528282</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.126914270738059</v>
+        <v>-1.161062471611845</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.70384515397988</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.509606246427105</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64248703814195</v>
+        <v>-10.72785754032641</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.125437900755495</v>
+        <v>-1.159586101629281</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.70384515397988</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.509606246427105</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84674521347181</v>
+        <v>-10.93211571565628</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.201627973768798</v>
+        <v>-1.235776174642584</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.831484098593869</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.438536076777354</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06478298510299</v>
+        <v>-11.15015348728745</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.284360527936834</v>
+        <v>-1.318508728810619</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.920884364505305</v>
+        <v>-3.006254866689768</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.389378471714928</v>
+        <v>1.33815617040425</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99131315343554</v>
+        <v>-11.07668365562001</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.239600893776433</v>
+        <v>-1.273749094650218</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.847414532837857</v>
+        <v>-2.93278503502232</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.448832072208818</v>
+        <v>1.397609770898141</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16643757082209</v>
+        <v>-11.25180807300655</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.295095439983533</v>
+        <v>-1.329243640857319</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.107909452408864</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.358312642524409</v>
+        <v>1.307090341213731</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40088966483658</v>
+        <v>-11.48626016702104</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.396095442490925</v>
+        <v>-1.43024364336471</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.107909452408864</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.351093477622813</v>
+        <v>1.299871176312135</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.68869350937381</v>
+        <v>-11.77406401155828</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.517889171079796</v>
+        <v>-1.552037371953582</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.310342794761639</v>
+        <v>-3.395713296946102</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.171738980126494</v>
+        <v>1.120516678815816</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91851795653764</v>
+        <v>-12.0038884587221</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.608703160106771</v>
+        <v>-1.642851360980556</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.472990331831799</v>
+        <v>-3.558360834016262</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.075266247722954</v>
+        <v>1.024043946412276</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.1505468762739</v>
+        <v>-12.23591737845836</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.698820999372161</v>
+        <v>-1.732969200245946</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.620373531204685</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.040752358039014</v>
+        <v>0.9895300567283365</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09853136230509</v>
+        <v>-12.18390186448955</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.674024458098234</v>
+        <v>-1.70817265897202</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.620373531204685</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.044742693725415</v>
+        <v>0.9935203924147373</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24020320402921</v>
+        <v>-12.32557370621367</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.732168421686624</v>
+        <v>-1.76631662256041</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.620373531204685</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.043267466826673</v>
+        <v>0.9920451655159956</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.33910994448848</v>
+        <v>-12.42448044667295</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.756677707705462</v>
+        <v>-1.790825908579248</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.633909769479498</v>
+        <v>-3.719280271663961</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9989768327159809</v>
+        <v>0.9477545314053031</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.13995783725139</v>
+        <v>-12.22532833943585</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.690067998457306</v>
+        <v>-1.724216199331091</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.468587243529684</v>
+        <v>-3.553957745714147</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.085119214639186</v>
+        <v>1.033896913328508</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.91411268453198</v>
+        <v>-11.99948318671644</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.590150864333333</v>
+        <v>-1.624299065207118</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.512031070126984</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.119854293027692</v>
+        <v>1.068631991717015</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.62783787220928</v>
+        <v>-11.71320837439374</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.474501794848196</v>
+        <v>-1.508649995721982</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.512031070126984</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.120993437583751</v>
+        <v>1.069771136273074</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68073316025357</v>
+        <v>-11.76610366243803</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.493026135903803</v>
+        <v>-1.527174336777589</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.507075724038538</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.126600419398927</v>
+        <v>1.075378118088249</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39682442932482</v>
+        <v>-11.48219493150928</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.373728939293667</v>
+        <v>-1.407877140167453</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.507075724038538</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.132334123637563</v>
+        <v>1.081111822326886</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.14983717913187</v>
+        <v>-11.23520768131633</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.284671301610351</v>
+        <v>-1.318819502484137</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.260088473845586</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.270789211359469</v>
+        <v>1.219566910048792</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.8860003119278</v>
+        <v>-10.97137081411226</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.189020036041631</v>
+        <v>-1.223168236915417</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.260088473845586</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.260905730046562</v>
+        <v>1.209683428735884</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6187585110594</v>
+        <v>-10.70412901324386</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.083957876193646</v>
+        <v>-1.118106077067431</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.174717971661122</v>
+        <v>-3.260088473845586</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.259071169547188</v>
+        <v>1.20784886823651</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.34294934765891</v>
+        <v>-10.42831984984338</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.973934525806913</v>
+        <v>-1.008082726680698</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.085698663382389</v>
+        <v>-3.171069165566852</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.312182439540967</v>
+        <v>1.26096013823029</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.31899580668296</v>
+        <v>-10.40436630886742</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.963684603271036</v>
+        <v>-0.9978328041448212</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.061745122406431</v>
+        <v>-3.147115624590894</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.327223070272036</v>
+        <v>1.276000768961358</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.05493586836016</v>
+        <v>-10.14030637054462</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8713209441036689</v>
+        <v>-0.905469144977455</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.883055686268098</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.472398717103961</v>
+        <v>1.421176415793283</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.347856244855322</v>
+        <v>-9.433226747039784</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5912761283620354</v>
+        <v>-0.6254243292358206</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.883055686268098</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.46961168344366</v>
+        <v>1.418389382132982</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.307671946489132</v>
+        <v>-9.393042448673594</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5748587851277178</v>
+        <v>-0.609006986001503</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.757500885717445</v>
+        <v>-2.842871387901908</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.494065886351216</v>
+        <v>1.442843585040538</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.227602150951327</v>
+        <v>-9.312972653135789</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5434640456918389</v>
+        <v>-0.5776122465656246</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.677431090179641</v>
+        <v>-2.762801592364104</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.541474584894655</v>
+        <v>1.490252283583977</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.994120928721728</v>
+        <v>-9.07949143090619</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4421471279621469</v>
+        <v>-0.4762953288359322</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.443949867950042</v>
+        <v>-2.529320370134505</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.689487747070267</v>
+        <v>1.638265445759589</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.814412398577854</v>
+        <v>-8.899782900762316</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3731559262175566</v>
+        <v>-0.4073041270913422</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.386778363787346</v>
+        <v>-2.472148865971809</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.720898439254925</v>
+        <v>1.669676137944247</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.682136924946967</v>
+        <v>-8.767507427131429</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3248782500181746</v>
+        <v>-0.3590264508919603</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.25450289015646</v>
+        <v>-2.339873392340923</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.795631210180484</v>
+        <v>1.744408908869806</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.491537250273813</v>
+        <v>-8.576907752458276</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2458233194612767</v>
+        <v>-0.2799715203350619</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.14927371766777</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.912806075672012</v>
+        <v>1.861583774361334</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.242537451590232</v>
+        <v>-8.327907953774695</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1333170587641854</v>
+        <v>-0.1674652596379711</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.063903215483307</v>
+        <v>-2.14927371766777</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.925712416895671</v>
+        <v>1.874490115584993</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.348127441363337</v>
+        <v>-8.433497943547799</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3035289842726456</v>
+        <v>-0.3376771851464313</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.254863707440875</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.73438249343259</v>
+        <v>1.683160192121912</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.366862343481934</v>
+        <v>-8.452232845666396</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2624786032429984</v>
+        <v>-0.2966268041167837</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.169493205256412</v>
+        <v>-2.254863707440875</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.782926835309676</v>
+        <v>1.731704533998998</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.090124168811121</v>
+        <v>-8.175494670995583</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1484043213886785</v>
+        <v>-0.1825525222624642</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.987676544146486</v>
+        <v>-2.073047046330949</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.895395843961626</v>
+        <v>1.844173542650948</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.963231762376051</v>
+        <v>-8.048602264560513</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1063613450681284</v>
+        <v>-0.1405095459419141</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.946154639895879</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.96281730156919</v>
+        <v>1.911595000258512</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.91968335560536</v>
+        <v>-8.005053857789822</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09590259445494542</v>
+        <v>-0.1300507953287311</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.946154639895879</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.955856689474097</v>
+        <v>1.904634388163419</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.677534962151502</v>
+        <v>-7.762905464335963</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01541911730774093</v>
+        <v>-0.01872908356604475</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.946154639895879</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.97031904385524</v>
+        <v>1.919096742544562</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.507695563948653</v>
+        <v>-7.699676092567615</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07788699704807556</v>
+        <v>0.001094785600489701</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.860784137711416</v>
+        <v>-1.946154639895879</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.964851164314435</v>
+        <v>1.913628863003757</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.321207871571647</v>
+        <v>-7.513188400190609</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1499801680094546</v>
+        <v>0.07318795656186872</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.67429644533441</v>
+        <v>-1.759666947518873</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.074241873751216</v>
+        <v>2.023019572440538</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.300058672668204</v>
+        <v>-7.492039201287166</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1661408258081578</v>
+        <v>0.08934861436057195</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.738517748615429</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.094632371330607</v>
+        <v>2.043410070019929</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.056293230684759</v>
+        <v>-7.248273759303721</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2594277109485863</v>
+        <v>0.1826354995010004</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.653147246430966</v>
+        <v>-1.738517748615429</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.090413079677658</v>
+        <v>2.03919077836698</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.7922651634915</v>
+        <v>-6.984245692110462</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.367163251745906</v>
+        <v>0.2903710402983202</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.536652349799476</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.213656632887246</v>
+        <v>2.162434331576568</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.542414769542425</v>
+        <v>-6.734395298161387</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4598454843092381</v>
+        <v>0.3830532728616522</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.536652349799476</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.206398707870948</v>
+        <v>2.15517640656027</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.238847280538447</v>
+        <v>-6.430827809157408</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5848716034314783</v>
+        <v>0.5080793919838924</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.451281847615013</v>
+        <v>-1.536652349799476</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.209997831391597</v>
+        <v>2.158775530080919</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.165367371686433</v>
+        <v>-6.357347900305395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6275910730268373</v>
+        <v>0.5507988615792514</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.377801938762998</v>
+        <v>-1.463172440947461</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.267413282757359</v>
+        <v>2.216190981446681</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.94033437201761</v>
+        <v>-6.132314900636572</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7166247505106638</v>
+        <v>0.6398325390630779</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.152768939094175</v>
+        <v>-1.238139441278638</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.40145356017495</v>
+        <v>2.350231258864272</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.725699994381203</v>
+        <v>-5.917680523000165</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8071733026195438</v>
+        <v>0.7303810911719579</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.023505063642232</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.534928987811111</v>
+        <v>2.483706686500434</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.459099637406851</v>
+        <v>-5.651080166025813</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.89500770419308</v>
+        <v>0.8182154927454941</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9381345614577685</v>
+        <v>-1.023505063642232</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.516123246594907</v>
+        <v>2.464900945284229</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.218669140601991</v>
+        <v>-5.410649669220953</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9929229795399017</v>
+        <v>0.9161307680923159</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.7830745668373713</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.6621246213027</v>
+        <v>2.610902319992022</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.975878332952545</v>
+        <v>-5.167858861571507</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.0939686164345</v>
+        <v>1.017176404986914</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6977040646529082</v>
+        <v>-0.7830745668373713</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.666053935137521</v>
+        <v>2.614831633826843</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.736273241345456</v>
+        <v>-4.928253769964418</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.190489236994676</v>
+        <v>1.11369702554709</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.7160266191688768</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.706961287655957</v>
+        <v>2.65573898634528</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.493617652922293</v>
+        <v>-4.685598181541255</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.284549543583934</v>
+        <v>1.207757332136349</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6306561169844137</v>
+        <v>-0.7160266191688768</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.703959358875951</v>
+        <v>2.652737057565273</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.273596854885282</v>
+        <v>-4.465577383504244</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.374136899809353</v>
+        <v>1.297344688361767</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.5748067741008965</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.790270302927353</v>
+        <v>2.739048001616675</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.074348224980473</v>
+        <v>-4.266328753599435</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.4697305345731</v>
+        <v>1.392938323125514</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4894362719164335</v>
+        <v>-0.5748067741008965</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.806164485729176</v>
+        <v>2.754942184418498</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.914833121461103</v>
+        <v>-4.106813650080065</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.53468242042115</v>
+        <v>1.457890208973564</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3299211683970635</v>
+        <v>-0.4152916705815266</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.9030193922811</v>
+        <v>2.851797090970422</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.770160976361366</v>
+        <v>-3.962141504980328</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.602639381022484</v>
+        <v>1.525847169574899</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1852490232973261</v>
+        <v>-0.2706195254817892</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.999910781902383</v>
+        <v>2.948688480591705</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,45 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.763576486342096</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.75239151743041</v>
+        <v>-3.970362615744228</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.525086856681588</v>
+        <v>1.43789841735606</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1674795643663706</v>
+        <v>-0.2788406362456895</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.925912149347678</v>
+        <v>2.859095506220086</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="2" t="n">
+        <v>45396</v>
+      </c>
+      <c r="B1934" t="n">
+        <v>3.553165131290338</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>2.991495414174943</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>-3.970362615744228</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>1.43789841735606</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>-0.2788406362456895</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>2.984559211161311</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.5%</t>
+          <t>137.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.7%</t>
+          <t>-56.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>662.0%</t>
+          <t>502.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-558.6%</t>
+          <t>-525.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-44.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-195.0%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-232.4%</t>
+          <t>-219.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-315.1%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-152.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-251.9%</t>
+          <t>-245.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-189.5%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-147.6%</t>
+          <t>-133.9%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4367914390125668</v>
+        <v>0.52216194119703</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.296930323404222</v>
+        <v>3.331078524278007</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.733020662456745</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.16238256958699</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1996599471627717</v>
+        <v>0.4424662765928274</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.237018811161846</v>
+        <v>3.334141342933868</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.733020662456745</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.197323654084531</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2046975378903583</v>
+        <v>0.447503867320414</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.237611287638218</v>
+        <v>3.334733819410241</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.788665118723062</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.229287768029661</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1482279067140615</v>
+        <v>0.3910342361441172</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.193769816791437</v>
+        <v>3.290892348563459</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.732195487546766</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.174152370947619</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08246051666464943</v>
+        <v>0.3252668460947051</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.168480469902142</v>
+        <v>3.265603001674164</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.732195487546766</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.175169980078089</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.06892503288793983</v>
+        <v>0.3117313623179955</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.153694308379214</v>
+        <v>3.250816840151236</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.732195487546766</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.165798012065845</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.01284686753981185</v>
+        <v>0.2299594618902439</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.111068274163352</v>
+        <v>3.208190805935374</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.759231060952902</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.172102082064765</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.08005597541168952</v>
+        <v>0.1627503540183662</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.088949947848303</v>
+        <v>3.186072479620325</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.759231060952902</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.176867398898468</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.07606452261649932</v>
+        <v>0.1667418068135564</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.088371325085619</v>
+        <v>3.185493856857641</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.763222513748092</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.177087066694822</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4938185461633363</v>
+        <v>-0.2510122167332806</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.919196607171948</v>
+        <v>3.01631913894397</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.345468490201255</v>
+        <v>1.430838992385719</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.924361544071783</v>
+        <v>3.975583845382461</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7154404797214537</v>
+        <v>-0.4726341502913981</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.830414050347622</v>
+        <v>2.927536582119645</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.307942356513886</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.901712080458283</v>
+        <v>3.952934381768961</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.923444538074531</v>
+        <v>-0.6806382086444753</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.752104571560317</v>
+        <v>2.849227103332339</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.307942356513886</v>
+        <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.906604225012209</v>
+        <v>3.957826526322886</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.193844500783416</v>
+        <v>-0.9510381713533607</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.639026042814751</v>
+        <v>2.736148574586773</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.037542393805001</v>
+        <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.739445703724865</v>
+        <v>3.790668005035543</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.533002878371938</v>
+        <v>-1.290196548941883</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.496446991085791</v>
+        <v>2.593569522857813</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6983840162164789</v>
+        <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.529034976478201</v>
+        <v>3.580257277788879</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.861020100099417</v>
+        <v>-1.618213770669362</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.385578392133568</v>
+        <v>2.48270092390559</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3703667944889998</v>
+        <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.352562933180482</v>
+        <v>3.40378523449116</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.354344971634595</v>
+        <v>-2.11153864220454</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.196347193928065</v>
+        <v>2.293469725700087</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2653806802493811</v>
+        <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.297670015045279</v>
+        <v>3.348892316355957</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.846729999658692</v>
+        <v>-2.603923670228637</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.000499574762158</v>
+        <v>2.097622106534181</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2270043477747157</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.003345390274553</v>
+        <v>3.054567691585231</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.231910390588765</v>
+        <v>-2.989104061158709</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.844969957202993</v>
+        <v>1.942092488975015</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2270043477747157</v>
+        <v>-0.1416338455902526</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.001887929087417</v>
+        <v>3.053110230398095</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.575593163815427</v>
+        <v>-3.332786834385371</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.709265971366944</v>
+        <v>1.806388503138966</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3349103998019339</v>
+        <v>-0.2495398976174708</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.938913421325702</v>
+        <v>2.99013572263638</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.933243514053775</v>
+        <v>-3.69043718462372</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.562311889927862</v>
+        <v>1.659434421699885</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6925607500402819</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.720429269838951</v>
+        <v>2.771651571149629</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.242477617049826</v>
+        <v>-3.99967128761977</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.440391175429702</v>
+        <v>1.537513707201724</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6925607500402819</v>
+        <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.72220219653921</v>
+        <v>2.773424497849888</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.674283410199613</v>
+        <v>-4.431477080769557</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.254001745637191</v>
+        <v>1.351124277409213</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8289782464815489</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.626684586141855</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.000715939067357</v>
+        <v>-4.757909609637301</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.111713509092184</v>
+        <v>1.208836040864206</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9114464969886971</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.565488410839657</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.336378586297809</v>
+        <v>-5.093572256867754</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9760290418559685</v>
+        <v>1.073151573627991</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9114464969886971</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.564069002495622</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.700004831198123</v>
+        <v>-5.457198501768067</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8370661041300846</v>
+        <v>0.9341886359021068</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.009668133855823</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.511623580609588</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.065132213836869</v>
+        <v>-5.822325884406814</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6902696660804173</v>
+        <v>0.7873921978524394</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.305978918154835</v>
+        <v>-1.220608415970372</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.333091625036012</v>
+        <v>2.38431392634669</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.473720991017548</v>
+        <v>-6.230914661587492</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5255956992229045</v>
+        <v>0.6227182309949271</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.086699902742364</v>
+        <v>2.137922204053042</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.886703475158642</v>
+        <v>-6.643897145728586</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3555881380379278</v>
+        <v>0.4527106698099503</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.081885335213824</v>
+        <v>2.133107636524502</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.303095349445639</v>
+        <v>-7.060289020015583</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1870254389320061</v>
+        <v>0.2841479707040286</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.079879385822702</v>
+        <v>2.13110168713338</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.679772359975484</v>
+        <v>-7.436966030545427</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0466133253887473</v>
+        <v>0.1437358571607699</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.090138076491381</v>
+        <v>2.141360377802059</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.025647181960291</v>
+        <v>-7.782840852530236</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09563703825948089</v>
+        <v>0.00148549351254168</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.086237641637076</v>
+        <v>2.137459942947754</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.33847198120527</v>
+        <v>-8.095665651775214</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2223620379024713</v>
+        <v>-0.1252395061304488</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.714567695335514</v>
+        <v>-1.629197193151051</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.084642561692077</v>
+        <v>2.135864863002755</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.635133323015468</v>
+        <v>-8.392326993585412</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3372475986973424</v>
+        <v>-0.2401250669253199</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.783310831069392</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.047175656180958</v>
+        <v>2.098397957491636</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.068482431125704</v>
+        <v>-8.825676101695647</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5146135464758395</v>
+        <v>-0.4174910147038169</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.783310831069392</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.043149351646555</v>
+        <v>2.094371652957232</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.451483819868335</v>
+        <v>-9.208677490438278</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6679162032944763</v>
+        <v>-0.5707936715224537</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.783310831069392</v>
+        <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.043047250324971</v>
+        <v>2.094269551635648</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.826469146039612</v>
+        <v>-9.583662816609555</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8153388177915568</v>
+        <v>-0.7182162860195342</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.15829615724067</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.820627570593634</v>
+        <v>1.871849871904312</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.18599946854361</v>
+        <v>-9.943193139113557</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9538006434951072</v>
+        <v>-0.8566781117230846</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.15829615724067</v>
+        <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.825977873891685</v>
+        <v>1.877200175202362</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.51239949720863</v>
+        <v>-10.26959316777857</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.076444635003935</v>
+        <v>-0.9793221032319122</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.484696185905683</v>
+        <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.638053876649854</v>
+        <v>1.689276177960532</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.73154846528282</v>
+        <v>-10.48874213585277</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.161062471611845</v>
+        <v>-1.063939939839823</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.70384515397988</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.509606246427105</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.72785754032641</v>
+        <v>-10.48505121089636</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.159586101629281</v>
+        <v>-1.062463569857258</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.70384515397988</v>
+        <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.509606246427105</v>
+        <v>1.560828547737782</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.93211571565628</v>
+        <v>-10.68930938622622</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.235776174642584</v>
+        <v>-1.138653642870562</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.831484098593869</v>
+        <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.438536076777354</v>
+        <v>1.489758378088031</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.15015348728745</v>
+        <v>-10.9073471578574</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.318508728810619</v>
+        <v>-1.221386197038596</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.006254866689768</v>
+        <v>-2.920884364505305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.33815617040425</v>
+        <v>1.389378471714928</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.07668365562001</v>
+        <v>-10.83387732618995</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.273749094650218</v>
+        <v>-1.176626562878195</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.93278503502232</v>
+        <v>-2.847414532837857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.397609770898141</v>
+        <v>1.448832072208818</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.25180807300655</v>
+        <v>-11.00900174357649</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.329243640857319</v>
+        <v>-1.232121109085297</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.107909452408864</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.307090341213731</v>
+        <v>1.358312642524409</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.48626016702104</v>
+        <v>-11.24345383759098</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.43024364336471</v>
+        <v>-1.333121111592688</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.107909452408864</v>
+        <v>-3.0225389502244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.299871176312135</v>
+        <v>1.351093477622813</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.77406401155828</v>
+        <v>-11.53125768212822</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.552037371953582</v>
+        <v>-1.45491484018156</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.395713296946102</v>
+        <v>-3.310342794761639</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.120516678815816</v>
+        <v>1.171738980126494</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.0038884587221</v>
+        <v>-11.76108212929205</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.642851360980556</v>
+        <v>-1.545728829208533</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.558360834016262</v>
+        <v>-3.472990331831799</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.024043946412276</v>
+        <v>1.075266247722954</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.23591737845836</v>
+        <v>-11.99311104902831</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.732969200245946</v>
+        <v>-1.635846668473924</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.620373531204685</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9895300567283365</v>
+        <v>1.040752358039014</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.18390186448955</v>
+        <v>-11.94109553505949</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.70817265897202</v>
+        <v>-1.611050127199998</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.620373531204685</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9935203924147373</v>
+        <v>1.044742693725415</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.32557370621367</v>
+        <v>-12.08276737678361</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.76631662256041</v>
+        <v>-1.669194090788388</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.620373531204685</v>
+        <v>-3.535003029020222</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9920451655159956</v>
+        <v>1.043267466826673</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.42448044667295</v>
+        <v>-12.18167411724289</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.790825908579248</v>
+        <v>-1.693703376807225</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.719280271663961</v>
+        <v>-3.633909769479498</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9477545314053031</v>
+        <v>0.9989768327159809</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.22532833943585</v>
+        <v>-11.98252201000579</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.724216199331091</v>
+        <v>-1.627093667559068</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.553957745714147</v>
+        <v>-3.468587243529684</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.033896913328508</v>
+        <v>1.085119214639186</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.99948318671644</v>
+        <v>-11.75667685728638</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.624299065207118</v>
+        <v>-1.527176533435096</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.512031070126984</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.068631991717015</v>
+        <v>1.119854293027692</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.71320837439374</v>
+        <v>-11.47040204496369</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.508649995721982</v>
+        <v>-1.411527463949959</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.512031070126984</v>
+        <v>-3.426660567942521</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.069771136273074</v>
+        <v>1.120993437583751</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.76610366243803</v>
+        <v>-11.52329733300797</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.527174336777589</v>
+        <v>-1.430051805005566</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.507075724038538</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.075378118088249</v>
+        <v>1.126600419398927</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.48219493150928</v>
+        <v>-11.23938860207922</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.407877140167453</v>
+        <v>-1.31075460839543</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.507075724038538</v>
+        <v>-3.421705221854074</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.081111822326886</v>
+        <v>1.132334123637563</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.23520768131633</v>
+        <v>-10.99240135188627</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.318819502484137</v>
+        <v>-1.221696970712115</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.260088473845586</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.219566910048792</v>
+        <v>1.270789211359469</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.97137081411226</v>
+        <v>-10.7285644846822</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.223168236915417</v>
+        <v>-1.126045705143394</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.260088473845586</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.209683428735884</v>
+        <v>1.260905730046562</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.70412901324386</v>
+        <v>-10.4613226838138</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.118106077067431</v>
+        <v>-1.020983545295409</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.260088473845586</v>
+        <v>-3.174717971661122</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.20784886823651</v>
+        <v>1.259071169547188</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.42831984984338</v>
+        <v>-10.18551352041332</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.008082726680698</v>
+        <v>-0.9109601949086756</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.171069165566852</v>
+        <v>-3.085698663382389</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.26096013823029</v>
+        <v>1.312182439540967</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.40436630886742</v>
+        <v>-10.16155997943736</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9978328041448212</v>
+        <v>-0.9007102723727987</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.147115624590894</v>
+        <v>-3.061745122406431</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.276000768961358</v>
+        <v>1.327223070272036</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.14030637054462</v>
+        <v>-9.897500041114565</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.905469144977455</v>
+        <v>-0.8083466132054324</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.883055686268098</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.421176415793283</v>
+        <v>1.472398717103961</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.433226747039784</v>
+        <v>-9.190420417609728</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6254243292358206</v>
+        <v>-0.528301797463798</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.883055686268098</v>
+        <v>-2.797685184083635</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.418389382132982</v>
+        <v>1.46961168344366</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.393042448673594</v>
+        <v>-9.150236119243537</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.609006986001503</v>
+        <v>-0.5118844542294805</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.842871387901908</v>
+        <v>-2.757500885717445</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.442843585040538</v>
+        <v>1.494065886351216</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.312972653135789</v>
+        <v>-9.070166323705733</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5776122465656246</v>
+        <v>-0.480489714793602</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.762801592364104</v>
+        <v>-2.677431090179641</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.490252283583977</v>
+        <v>1.541474584894655</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.07949143090619</v>
+        <v>-8.836685101476133</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4762953288359322</v>
+        <v>-0.3791727970639096</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.529320370134505</v>
+        <v>-2.443949867950042</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.638265445759589</v>
+        <v>1.689487747070267</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.899782900762316</v>
+        <v>-8.65697657133226</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4073041270913422</v>
+        <v>-0.3101815953193197</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.472148865971809</v>
+        <v>-2.386778363787346</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.669676137944247</v>
+        <v>1.720898439254925</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.767507427131429</v>
+        <v>-8.524701097701373</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3590264508919603</v>
+        <v>-0.2619039191199377</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.339873392340923</v>
+        <v>-2.25450289015646</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.744408908869806</v>
+        <v>1.795631210180484</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.576907752458276</v>
+        <v>-8.377358292342649</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2799715203350619</v>
+        <v>-0.2001517362888112</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.14927371766777</v>
+        <v>-2.107160084797735</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.861583774361334</v>
+        <v>1.886851954083355</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.327907953774695</v>
+        <v>-8.128358493659068</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1674652596379711</v>
+        <v>-0.08764547559172042</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.14927371766777</v>
+        <v>-2.107160084797735</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.874490115584993</v>
+        <v>1.899758295307014</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.433497943547799</v>
+        <v>-8.233948483432172</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3376771851464313</v>
+        <v>-0.2578574011001806</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.254863707440875</v>
+        <v>-2.212750074570839</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.683160192121912</v>
+        <v>1.708428371843933</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.452232845666396</v>
+        <v>-8.252683385550769</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2966268041167837</v>
+        <v>-0.216807020070533</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.254863707440875</v>
+        <v>-2.212750074570839</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.731704533998998</v>
+        <v>1.756972713721019</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.175494670995583</v>
+        <v>-7.975945210879956</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1825525222624642</v>
+        <v>-0.1027327382162135</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.073047046330949</v>
+        <v>-2.030933413460914</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.844173542650948</v>
+        <v>1.869441722372969</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.048602264560513</v>
+        <v>-7.849052804444886</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1405095459419141</v>
+        <v>-0.06068976189566344</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.946154639895879</v>
+        <v>-1.904041007025844</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.911595000258512</v>
+        <v>1.936863179980533</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.005053857789822</v>
+        <v>-7.805504397674196</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1300507953287311</v>
+        <v>-0.05023101128248042</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.946154639895879</v>
+        <v>-1.904041007025844</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.904634388163419</v>
+        <v>1.92990256788544</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.762905464335963</v>
+        <v>-7.563356004220338</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01872908356604475</v>
+        <v>0.06109070048020593</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.946154639895879</v>
+        <v>-1.904041007025844</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.919096742544562</v>
+        <v>1.944364922266583</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.699676092567615</v>
+        <v>-7.393516606017489</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.001094785600489701</v>
+        <v>0.1235585802205406</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.946154639895879</v>
+        <v>-1.904041007025844</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.913628863003757</v>
+        <v>1.938897042725778</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.513188400190609</v>
+        <v>-7.207028913640483</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.07318795656186872</v>
+        <v>0.19565175118192</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.759666947518873</v>
+        <v>-1.717553314648838</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.023019572440538</v>
+        <v>2.048287752162559</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.492039201287166</v>
+        <v>-7.185879714737039</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08934861436057195</v>
+        <v>0.2118124089806228</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.738517748615429</v>
+        <v>-1.696404115745394</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.043410070019929</v>
+        <v>2.06867824974195</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.248273759303721</v>
+        <v>-6.942114272753595</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1826354995010004</v>
+        <v>0.3050992941210513</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.738517748615429</v>
+        <v>-1.696404115745394</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.03919077836698</v>
+        <v>2.064458958089001</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.984245692110462</v>
+        <v>-6.678086205560335</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2903710402983202</v>
+        <v>0.412834834918371</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.536652349799476</v>
+        <v>-1.494538716929441</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.162434331576568</v>
+        <v>2.187702511298589</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.734395298161387</v>
+        <v>-6.428235811611261</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3830532728616522</v>
+        <v>0.5055170674817031</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.536652349799476</v>
+        <v>-1.494538716929441</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.15517640656027</v>
+        <v>2.180444586282291</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.430827809157408</v>
+        <v>-6.124668322607282</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5080793919838924</v>
+        <v>0.6305431866039433</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.536652349799476</v>
+        <v>-1.494538716929441</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.158775530080919</v>
+        <v>2.18404370980294</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.357347900305395</v>
+        <v>-6.051188413755268</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5507988615792514</v>
+        <v>0.6732626561993027</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.463172440947461</v>
+        <v>-1.421058808077426</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.216190981446681</v>
+        <v>2.241459161168702</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.132314900636572</v>
+        <v>-5.826155414086445</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6398325390630779</v>
+        <v>0.7622963336831288</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.238139441278638</v>
+        <v>-1.196025808408603</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.350231258864272</v>
+        <v>2.375499438586293</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.917680523000165</v>
+        <v>-5.611521036450038</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7303810911719579</v>
+        <v>0.8528448857920088</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.023505063642232</v>
+        <v>-0.9813914307721965</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.483706686500434</v>
+        <v>2.508974866222454</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.651080166025813</v>
+        <v>-5.344920679475686</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8182154927454941</v>
+        <v>0.940679287365545</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.023505063642232</v>
+        <v>-0.9813914307721965</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.464900945284229</v>
+        <v>2.49016912500625</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.410649669220953</v>
+        <v>-5.104490182670826</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9161307680923159</v>
+        <v>1.038594562712367</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7830745668373713</v>
+        <v>-0.7409609339673362</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.610902319992022</v>
+        <v>2.636170499714044</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.167858861571507</v>
+        <v>-4.861699375021381</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.017176404986914</v>
+        <v>1.139640199606965</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7830745668373713</v>
+        <v>-0.7409609339673362</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.614831633826843</v>
+        <v>2.640099813548864</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.928253769964418</v>
+        <v>-4.622094283414292</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.11369702554709</v>
+        <v>1.236160820167141</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7160266191688768</v>
+        <v>-0.6739129862988417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.65573898634528</v>
+        <v>2.6810071660673</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.685598181541255</v>
+        <v>-4.379438694991128</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.207757332136349</v>
+        <v>1.330221126756399</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7160266191688768</v>
+        <v>-0.6739129862988417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652737057565273</v>
+        <v>2.678005237287294</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.465577383504244</v>
+        <v>-4.159417896954118</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.297344688361767</v>
+        <v>1.419808482981818</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5748067741008965</v>
+        <v>-0.5326931412308614</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.739048001616675</v>
+        <v>2.764316181338696</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.266328753599435</v>
+        <v>-3.960169267049308</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.392938323125514</v>
+        <v>1.515402117745565</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5748067741008965</v>
+        <v>-0.5326931412308614</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.754942184418498</v>
+        <v>2.78021036414052</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.106813650080065</v>
+        <v>-3.800654163529939</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.457890208973564</v>
+        <v>1.580354003593615</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4152916705815266</v>
+        <v>-0.3731780377114915</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.851797090970422</v>
+        <v>2.877065270692444</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.962141504980328</v>
+        <v>-3.655982018430201</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.525847169574899</v>
+        <v>1.64831096419495</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2706195254817892</v>
+        <v>-0.2285058926117541</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.948688480591705</v>
+        <v>2.973956660313726</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.970362615744228</v>
+        <v>-3.638212559499246</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.43789841735606</v>
+        <v>1.570758439854053</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2788406362456895</v>
+        <v>-0.2107364336807985</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.859095506220086</v>
+        <v>2.899958027759021</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.553165131290338</v>
+        <v>3.471267580076585</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.991495414174943</v>
+        <v>3.128005666179364</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.970362615744228</v>
+        <v>-3.638212559499246</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.43789841735606</v>
+        <v>1.570758439854053</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2788406362456895</v>
+        <v>-0.2107364336807985</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.984559211161311</v>
+        <v>3.121069463165731</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-15.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>138.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.8%</t>
+          <t>-57.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.7%</t>
+          <t>549.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-525.4%</t>
+          <t>-550.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.4%</t>
+          <t>-44.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>1059.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-219.1%</t>
+          <t>-229.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-245.1%</t>
+          <t>-243.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-133.9%</t>
+          <t>-150.9%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4424662765928274</v>
+        <v>0.2850304493472349</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.334141342933868</v>
+        <v>3.271167012035631</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.447503867320414</v>
+        <v>0.2900680400748214</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.334733819410241</v>
+        <v>3.271759488512004</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.3910342361441172</v>
+        <v>0.2335984088985246</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.290892348563459</v>
+        <v>3.227918017665222</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3252668460947051</v>
+        <v>0.1678310188491126</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.265603001674164</v>
+        <v>3.202628670775927</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3117313623179955</v>
+        <v>0.154295535072403</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.250816840151236</v>
+        <v>3.187842509252999</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2299594618902439</v>
+        <v>0.07252363464465128</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.208190805935374</v>
+        <v>3.145216475037137</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1627503540183662</v>
+        <v>0.005314526772773609</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.186072479620325</v>
+        <v>3.123098148722088</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1667418068135564</v>
+        <v>0.009305979567963807</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.185493856857641</v>
+        <v>3.122519525959405</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2510122167332806</v>
+        <v>-0.4084480439788732</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.01631913894397</v>
+        <v>2.953344808045733</v>
       </c>
       <c r="F1847" t="n">
         <v>1.430838992385719</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4726341502913981</v>
+        <v>-0.6300699775369907</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.927536582119645</v>
+        <v>2.864562251221408</v>
       </c>
       <c r="F1848" t="n">
         <v>1.393312858698349</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6806382086444753</v>
+        <v>-0.8380740358900679</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.849227103332339</v>
+        <v>2.786252772434102</v>
       </c>
       <c r="F1849" t="n">
         <v>1.393312858698349</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9510381713533607</v>
+        <v>-1.108473998598953</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.736148574586773</v>
+        <v>2.673174243688536</v>
       </c>
       <c r="F1850" t="n">
         <v>1.122912895989464</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.290196548941883</v>
+        <v>-1.447632376187475</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.593569522857813</v>
+        <v>2.530595191959576</v>
       </c>
       <c r="F1851" t="n">
         <v>0.783754518400942</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.618213770669362</v>
+        <v>-1.775649597914954</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.48270092390559</v>
+        <v>2.419726593007353</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4557372966734629</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.11153864220454</v>
+        <v>-2.268974469450132</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.293469725700087</v>
+        <v>2.23049539480185</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3507511824338441</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.603923670228637</v>
+        <v>-2.761359497474229</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.097622106534181</v>
+        <v>2.034647775635944</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.1416338455902526</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.989104061158709</v>
+        <v>-3.146539888404301</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.942092488975015</v>
+        <v>1.879118158076778</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.332786834385371</v>
+        <v>-3.490222661630964</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.806388503138966</v>
+        <v>1.743414172240729</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.69043718462372</v>
+        <v>-3.847873011869312</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.659434421699885</v>
+        <v>1.596460090801648</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.99967128761977</v>
+        <v>-4.157107114865363</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.537513707201724</v>
+        <v>1.474539376303487</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.431477080769557</v>
+        <v>-4.588912908015151</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.351124277409213</v>
+        <v>1.288149946510976</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.757909609637301</v>
+        <v>-4.915345436882895</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.208836040864206</v>
+        <v>1.145861709965969</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.093572256867754</v>
+        <v>-5.251008084113347</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.073151573627991</v>
+        <v>1.010177242729754</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.457198501768067</v>
+        <v>-5.61463432901366</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9341886359021068</v>
+        <v>0.8712143050038699</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.822325884406814</v>
+        <v>-5.979761711652407</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7873921978524394</v>
+        <v>0.7244178669542025</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.220608415970372</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.230914661587492</v>
+        <v>-6.388350488833085</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6227182309949271</v>
+        <v>0.5597439000966902</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.629197193151051</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.643897145728586</v>
+        <v>-6.801332972974179</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4527106698099503</v>
+        <v>0.3897363389117134</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.060289020015583</v>
+        <v>-7.217724847261176</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2841479707040286</v>
+        <v>0.2211736398057917</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.436966030545427</v>
+        <v>-7.594401857791021</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1437358571607699</v>
+        <v>0.08076152626253297</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.782840852530236</v>
+        <v>-7.940276679775829</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.00148549351254168</v>
+        <v>-0.06148883738569522</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.095665651775214</v>
+        <v>-8.253101479020808</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1252395061304488</v>
+        <v>-0.1882138370286857</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.392326993585412</v>
+        <v>-8.549762820831006</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2401250669253199</v>
+        <v>-0.3030993978235568</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.697940328884929</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.825676101695647</v>
+        <v>-8.983111928941241</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4174910147038169</v>
+        <v>-0.4804653456020542</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.208677490438278</v>
+        <v>-9.366113317683872</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5707936715224537</v>
+        <v>-0.6337680024206906</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.583662816609555</v>
+        <v>-9.74109864385515</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7182162860195342</v>
+        <v>-0.7811906169177711</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.943193139113557</v>
+        <v>-10.10062896635915</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8566781117230846</v>
+        <v>-0.919652442621322</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.26959316777857</v>
+        <v>-10.42702899502416</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9793221032319122</v>
+        <v>-1.042296434130149</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.48874213585277</v>
+        <v>-10.64617796309836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.063939939839823</v>
+        <v>-1.126914270738059</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.618474651795417</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.48505121089636</v>
+        <v>-10.64248703814195</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.062463569857258</v>
+        <v>-1.125437900755495</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.618474651795417</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.68930938622622</v>
+        <v>-10.84674521347181</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.138653642870562</v>
+        <v>-1.201627973768798</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.746113596409406</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.9073471578574</v>
+        <v>-11.06478298510299</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.221386197038596</v>
+        <v>-1.284360527936834</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.920884364505305</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.83387732618995</v>
+        <v>-10.99131315343554</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.176626562878195</v>
+        <v>-1.239600893776433</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.847414532837857</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.00900174357649</v>
+        <v>-11.16643757082209</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.232121109085297</v>
+        <v>-1.295095439983533</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.0225389502244</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.24345383759098</v>
+        <v>-11.40088966483658</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.333121111592688</v>
+        <v>-1.396095442490925</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.0225389502244</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.53125768212822</v>
+        <v>-11.68869350937381</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.45491484018156</v>
+        <v>-1.517889171079796</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.310342794761639</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.76108212929205</v>
+        <v>-11.91851795653764</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.545728829208533</v>
+        <v>-1.608703160106771</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.472990331831799</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.99311104902831</v>
+        <v>-12.1505468762739</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.635846668473924</v>
+        <v>-1.698820999372161</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.535003029020222</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.94109553505949</v>
+        <v>-12.09853136230509</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.611050127199998</v>
+        <v>-1.674024458098234</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.535003029020222</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.08276737678361</v>
+        <v>-12.24020320402921</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.669194090788388</v>
+        <v>-1.732168421686624</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.535003029020222</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.18167411724289</v>
+        <v>-12.33910994448848</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.693703376807225</v>
+        <v>-1.756677707705462</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.633909769479498</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.98252201000579</v>
+        <v>-12.13995783725139</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.627093667559068</v>
+        <v>-1.690067998457306</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.468587243529684</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.75667685728638</v>
+        <v>-11.91411268453198</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.527176533435096</v>
+        <v>-1.590150864333333</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.426660567942521</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.47040204496369</v>
+        <v>-11.62783787220928</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.411527463949959</v>
+        <v>-1.474501794848196</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.426660567942521</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.52329733300797</v>
+        <v>-11.68073316025357</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.430051805005566</v>
+        <v>-1.493026135903803</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.421705221854074</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.23938860207922</v>
+        <v>-11.39682442932482</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.31075460839543</v>
+        <v>-1.373728939293667</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.421705221854074</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.99240135188627</v>
+        <v>-11.14983717913187</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.221696970712115</v>
+        <v>-1.284671301610351</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.174717971661122</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.7285644846822</v>
+        <v>-10.8860003119278</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.126045705143394</v>
+        <v>-1.189020036041631</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.174717971661122</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.4613226838138</v>
+        <v>-10.6187585110594</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.020983545295409</v>
+        <v>-1.083957876193646</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.174717971661122</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.18551352041332</v>
+        <v>-10.34294934765891</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9109601949086756</v>
+        <v>-0.973934525806913</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.085698663382389</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.16155997943736</v>
+        <v>-10.31899580668296</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9007102723727987</v>
+        <v>-0.963684603271036</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.061745122406431</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.897500041114565</v>
+        <v>-10.05493586836016</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8083466132054324</v>
+        <v>-0.8713209441036689</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.797685184083635</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.190420417609728</v>
+        <v>-9.347856244855322</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.528301797463798</v>
+        <v>-0.5912761283620354</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.797685184083635</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.150236119243537</v>
+        <v>-9.307671946489132</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5118844542294805</v>
+        <v>-0.5748587851277178</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.757500885717445</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.070166323705733</v>
+        <v>-9.227602150951327</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.480489714793602</v>
+        <v>-0.5434640456918389</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.677431090179641</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.836685101476133</v>
+        <v>-8.994120928721728</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3791727970639096</v>
+        <v>-0.4421471279621469</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.443949867950042</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.65697657133226</v>
+        <v>-8.814412398577854</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3101815953193197</v>
+        <v>-0.3731559262175566</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.386778363787346</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.524701097701373</v>
+        <v>-8.682136924946967</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2619039191199377</v>
+        <v>-0.3248782500181746</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.25450289015646</v>
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.377358292342649</v>
+        <v>-8.520261684778166</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2001517362888112</v>
+        <v>-0.2573130932630177</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.107160084797735</v>
+        <v>-2.09262764998766</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.886851954083355</v>
+        <v>1.895571414969401</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.128358493659068</v>
+        <v>-8.271261886094585</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.08764547559172042</v>
+        <v>-0.1448068325659264</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.107160084797735</v>
+        <v>-2.09262764998766</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.899758295307014</v>
+        <v>1.908477756193059</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.233948483432172</v>
+        <v>-8.37685187586769</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2578574011001806</v>
+        <v>-0.3150187580743871</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.212750074570839</v>
+        <v>-2.198217639760764</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.708428371843933</v>
+        <v>1.717147832729978</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.252683385550769</v>
+        <v>-8.395586777986287</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.216807020070533</v>
+        <v>-0.2739683770447394</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.212750074570839</v>
+        <v>-2.198217639760764</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.756972713721019</v>
+        <v>1.765692174607064</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.975945210879956</v>
+        <v>-8.118848603315474</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1027327382162135</v>
+        <v>-0.1598940951904195</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.030933413460914</v>
+        <v>-2.016400978650839</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.869441722372969</v>
+        <v>1.878161183259014</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.849052804444886</v>
+        <v>-7.991956196880404</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06068976189566344</v>
+        <v>-0.1178511188698699</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.904041007025844</v>
+        <v>-1.889508572215769</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.936863179980533</v>
+        <v>1.945582640866578</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.805504397674196</v>
+        <v>-7.948407790109713</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05023101128248042</v>
+        <v>-0.1073923682566869</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.904041007025844</v>
+        <v>-1.889508572215769</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.92990256788544</v>
+        <v>1.938622028771485</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.563356004220338</v>
+        <v>-7.706259396655855</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06109070048020593</v>
+        <v>0.003929343505999494</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.904041007025844</v>
+        <v>-1.889508572215769</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.944364922266583</v>
+        <v>1.953084383152628</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.393516606017489</v>
+        <v>-7.643030024887507</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1235585802205406</v>
+        <v>0.02375321267253394</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.904041007025844</v>
+        <v>-1.889508572215769</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.938897042725778</v>
+        <v>1.947616503611823</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.207028913640483</v>
+        <v>-7.456542332510501</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.19565175118192</v>
+        <v>0.0958463836339134</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.717553314648838</v>
+        <v>-1.703020879838762</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.048287752162559</v>
+        <v>2.057007213048604</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.185879714737039</v>
+        <v>-7.435393133607057</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2118124089806228</v>
+        <v>0.1120070414326162</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.696404115745394</v>
+        <v>-1.681871680935319</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.06867824974195</v>
+        <v>2.077397710627995</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.942114272753595</v>
+        <v>-7.191627691623613</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3050992941210513</v>
+        <v>0.2052939265730447</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.696404115745394</v>
+        <v>-1.681871680935319</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.064458958089001</v>
+        <v>2.073178418975046</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.678086205560335</v>
+        <v>-6.927599624430353</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.412834834918371</v>
+        <v>0.3130294673703644</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.494538716929441</v>
+        <v>-1.480006282119366</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.187702511298589</v>
+        <v>2.196421972184634</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.428235811611261</v>
+        <v>-6.677749230481279</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5055170674817031</v>
+        <v>0.4057116999336965</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.494538716929441</v>
+        <v>-1.480006282119366</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.180444586282291</v>
+        <v>2.189164047168336</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.124668322607282</v>
+        <v>-6.3741817414773</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6305431866039433</v>
+        <v>0.5307378190559366</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.494538716929441</v>
+        <v>-1.480006282119366</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.18404370980294</v>
+        <v>2.192763170688985</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.051188413755268</v>
+        <v>-6.300701832625286</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6732626561993027</v>
+        <v>0.5734572886512961</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.421058808077426</v>
+        <v>-1.406526373267351</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.241459161168702</v>
+        <v>2.250178622054747</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.826155414086445</v>
+        <v>-6.075668832956463</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7622963336831288</v>
+        <v>0.6624909661351222</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.196025808408603</v>
+        <v>-1.181493373598528</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.375499438586293</v>
+        <v>2.384218899472338</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.611521036450038</v>
+        <v>-5.861034455320056</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8528448857920088</v>
+        <v>0.7530395182440022</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9813914307721965</v>
+        <v>-0.9668589959621214</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.508974866222454</v>
+        <v>2.517694327108499</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.344920679475686</v>
+        <v>-5.594434098345705</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.940679287365545</v>
+        <v>0.8408739198175388</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9813914307721965</v>
+        <v>-0.9668589959621214</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.49016912500625</v>
+        <v>2.498888585892295</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.104490182670826</v>
+        <v>-5.354003601540844</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.038594562712367</v>
+        <v>0.9387891951643601</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7409609339673362</v>
+        <v>-0.7264284991572612</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.636170499714044</v>
+        <v>2.644889960600089</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.861699375021381</v>
+        <v>-5.111212793891399</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.139640199606965</v>
+        <v>1.039834832058959</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7409609339673362</v>
+        <v>-0.7264284991572612</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.640099813548864</v>
+        <v>2.648819274434909</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.622094283414292</v>
+        <v>-4.87160770228431</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.236160820167141</v>
+        <v>1.136355452619134</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6739129862988417</v>
+        <v>-0.6593805514887666</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.6810071660673</v>
+        <v>2.689726626953346</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.379438694991128</v>
+        <v>-4.628952113861146</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.330221126756399</v>
+        <v>1.230415759208393</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6739129862988417</v>
+        <v>-0.6593805514887666</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678005237287294</v>
+        <v>2.686724698173339</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.159417896954118</v>
+        <v>-4.408931315824136</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.419808482981818</v>
+        <v>1.320003115433811</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5326931412308614</v>
+        <v>-0.5181607064207864</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.764316181338696</v>
+        <v>2.773035642224742</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.960169267049308</v>
+        <v>-4.209682685919327</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.515402117745565</v>
+        <v>1.415596750197558</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5326931412308614</v>
+        <v>-0.5181607064207864</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.78021036414052</v>
+        <v>2.788929825026565</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.800654163529939</v>
+        <v>-4.050167582399957</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.580354003593615</v>
+        <v>1.480548636045608</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3731780377114915</v>
+        <v>-0.3586456029014164</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877065270692444</v>
+        <v>2.885784731578489</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.655982018430201</v>
+        <v>-3.905495437300219</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.64831096419495</v>
+        <v>1.548505596646943</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2285058926117541</v>
+        <v>-0.213973457801679</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.973956660313726</v>
+        <v>2.982676121199771</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.638212559499246</v>
+        <v>-3.887725978369264</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.570758439854053</v>
+        <v>1.470953072306047</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2107364336807985</v>
+        <v>-0.1962039988707235</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.899958027759021</v>
+        <v>2.908677488645066</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.471267580076585</v>
+        <v>3.471267580076584</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.128005666179364</v>
+        <v>2.958264385201043</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.638212559499246</v>
+        <v>-3.887725978369264</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.570758439854053</v>
+        <v>1.470953072306047</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2107364336807985</v>
+        <v>-0.1962039988707235</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.121069463165731</v>
+        <v>2.951328182187411</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.4%</t>
+          <t>137.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-700.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.4%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>549.2%</t>
+          <t>550.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-550.3%</t>
+          <t>-507.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-274.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.9%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1059.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-229.1%</t>
+          <t>-200.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.2%</t>
+          <t>-152.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-243.6%</t>
+          <t>-205.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>51.7%</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-174.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-150.9%</t>
+          <t>-120.2%</t>
         </is>
       </c>
     </row>
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.255211538113584</v>
       </c>
       <c r="D1840" t="n">
         <v>0.2900680400748214</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.271759488512004</v>
+        <v>3.370882329829765</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.379632910658099</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.233957919737321</v>
       </c>
       <c r="D1841" t="n">
         <v>0.2335984088985246</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.227918017665222</v>
+        <v>3.327040858982983</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.324497513576058</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.234975528867791</v>
       </c>
       <c r="D1842" t="n">
         <v>0.1678310188491126</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.202628670775927</v>
+        <v>3.301751512093689</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.325515122706529</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.225603560855546</v>
       </c>
       <c r="D1843" t="n">
         <v>0.154295535072403</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.187842509252999</v>
+        <v>3.28696535057076</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.316143154694284</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.215686286810785</v>
       </c>
       <c r="D1844" t="n">
         <v>0.07252363464465128</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.145216475037137</v>
+        <v>3.244339316354898</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.322447224693204</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.220451603644487</v>
       </c>
       <c r="D1845" t="n">
         <v>0.005314526772773609</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.123098148722088</v>
+        <v>3.222220990039849</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.327212541526906</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.218276399763727</v>
       </c>
       <c r="D1846" t="n">
         <v>0.009305979567963807</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.122519525959405</v>
+        <v>3.221642367277166</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.327432209323261</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.216203291268791</v>
       </c>
       <c r="D1847" t="n">
         <v>-0.4084480439788732</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.953344808045733</v>
+        <v>3.052467649363494</v>
       </c>
       <c r="F1847" t="n">
         <v>1.430838992385719</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.975583845382461</v>
+        <v>4.074706686700222</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.216069507867712</v>
       </c>
       <c r="D1848" t="n">
         <v>-0.6300699775369907</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.864562251221408</v>
+        <v>2.963685092539169</v>
       </c>
       <c r="F1848" t="n">
         <v>1.393312858698349</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.952934381768961</v>
+        <v>4.052057223086722</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.220961652421638</v>
       </c>
       <c r="D1849" t="n">
         <v>-0.8380740358900679</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.786252772434102</v>
+        <v>2.885375613751863</v>
       </c>
       <c r="F1849" t="n">
         <v>1.393312858698349</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.957826526322886</v>
+        <v>4.056949367640647</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.216043108759626</v>
       </c>
       <c r="D1850" t="n">
         <v>-1.108473998598953</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.673174243688536</v>
+        <v>2.772297085006297</v>
       </c>
       <c r="F1850" t="n">
         <v>1.122912895989464</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.790668005035543</v>
+        <v>3.889790846353304</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.209127408066075</v>
       </c>
       <c r="D1851" t="n">
         <v>-1.447632376187475</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.530595191959576</v>
+        <v>2.629718033277337</v>
       </c>
       <c r="F1851" t="n">
         <v>0.783754518400942</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.580257277788879</v>
+        <v>3.67938011910664</v>
       </c>
     </row>
     <row r="1852">
@@ -44144,19 +44144,19 @@
         <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.229465697804843</v>
       </c>
       <c r="D1852" t="n">
         <v>-1.775649597914954</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.419726593007353</v>
+        <v>2.518849434325114</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4557372966734629</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.40378523449116</v>
+        <v>3.502908075808921</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.237564448213412</v>
       </c>
       <c r="D1853" t="n">
         <v>-2.268974469450132</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.23049539480185</v>
+        <v>2.329618236119612</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3507511824338441</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.348892316355957</v>
+        <v>3.448015157673719</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.238670840257144</v>
       </c>
       <c r="D1854" t="n">
         <v>-2.761359497474229</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.034647775635944</v>
+        <v>2.133770616953705</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.1416338455902526</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.054567691585231</v>
+        <v>3.153690532902993</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.237213379070008</v>
       </c>
       <c r="D1855" t="n">
         <v>-3.146539888404301</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.879118158076778</v>
+        <v>1.97824099939454</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.053110230398095</v>
+        <v>3.152233071715856</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.238982502524624</v>
       </c>
       <c r="D1856" t="n">
         <v>-3.490222661630964</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.743414172240729</v>
+        <v>1.842537013558491</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>3.089258563954142</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.235088561180882</v>
       </c>
       <c r="D1857" t="n">
         <v>-3.847873011869312</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.596460090801648</v>
+        <v>1.695582932119409</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.87077441246739</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.236861487881141</v>
       </c>
       <c r="D1858" t="n">
         <v>-4.157107114865363</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.474539376303487</v>
+        <v>1.573662217621248</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.87254733916765</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.223194375348545</v>
       </c>
       <c r="D1859" t="n">
         <v>-4.588912908015151</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.288149946510976</v>
+        <v>1.387272787828738</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.777029728770294</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.211479150350636</v>
       </c>
       <c r="D1860" t="n">
         <v>-4.915345436882895</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.145861709965969</v>
+        <v>1.244984551283731</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.715833553468096</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.210059742006601</v>
       </c>
       <c r="D1861" t="n">
         <v>-5.251008084113347</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.010177242729754</v>
+        <v>1.109300084047515</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.714414145124061</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.216547302240843</v>
       </c>
       <c r="D1862" t="n">
         <v>-5.61463432901366</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8712143050038699</v>
+        <v>0.9703371463216315</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.661968723238027</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.215801817246674</v>
       </c>
       <c r="D1863" t="n">
         <v>-5.979761711652407</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7244178669542025</v>
+        <v>0.8235407082719641</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.220608415970372</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.38431392634669</v>
+        <v>2.483436767664451</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.214563361261433</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.388350488833085</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5597439000966902</v>
+        <v>0.6588667414144518</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.137922204053042</v>
+        <v>2.237045045370803</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.209748793732894</v>
       </c>
       <c r="D1865" t="n">
         <v>-6.801332972974179</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3897363389117134</v>
+        <v>0.4888591802294751</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.133107636524502</v>
+        <v>2.232230477842264</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.207742844341771</v>
       </c>
       <c r="D1866" t="n">
         <v>-7.217724847261176</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2211736398057917</v>
+        <v>0.3202964811235534</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.13110168713338</v>
+        <v>2.230224528451141</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.21800153501045</v>
       </c>
       <c r="D1867" t="n">
         <v>-7.594401857791021</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08076152626253297</v>
+        <v>0.1798843675802946</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.141360377802059</v>
+        <v>2.24048321911982</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.214101100156145</v>
       </c>
       <c r="D1868" t="n">
         <v>-7.940276679775829</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06148883738569522</v>
+        <v>0.0376340039320664</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.137459942947754</v>
+        <v>2.236582784265515</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.212506020211146</v>
       </c>
       <c r="D1869" t="n">
         <v>-8.253101479020808</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1882138370286857</v>
+        <v>-0.08909099571092405</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.629197193151051</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.135864863002755</v>
+        <v>2.234987704320516</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.216284996140355</v>
       </c>
       <c r="D1870" t="n">
         <v>-8.549762820831006</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3030993978235568</v>
+        <v>-0.2039765565057952</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.697940328884929</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.098397957491636</v>
+        <v>2.197520798809397</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.212258691605951</v>
       </c>
       <c r="D1871" t="n">
         <v>-8.983111928941241</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4804653456020542</v>
+        <v>-0.3813425042842926</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.697940328884929</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.094371652957232</v>
+        <v>2.193494494274994</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.212156590284367</v>
       </c>
       <c r="D1872" t="n">
         <v>-9.366113317683872</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6337680024206906</v>
+        <v>-0.534645161102929</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.697940328884929</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.094269551635648</v>
+        <v>2.19339239295341</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.214728106255798</v>
       </c>
       <c r="D1873" t="n">
         <v>-9.74109864385515</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7811906169177711</v>
+        <v>-0.6820677756000095</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.072925655056207</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.871849871904312</v>
+        <v>1.970972713222074</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.220078409553848</v>
       </c>
       <c r="D1874" t="n">
         <v>-10.10062896635915</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.919652442621322</v>
+        <v>-0.8205296013035603</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.072925655056207</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.877200175202362</v>
+        <v>1.976323016520124</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.227994429511025</v>
       </c>
       <c r="D1875" t="n">
         <v>-10.42702899502416</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.042296434130149</v>
+        <v>-0.9431735928123879</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.39932568372122</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.689276177960532</v>
+        <v>1.788399019278294</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.231036180132794</v>
       </c>
       <c r="D1876" t="n">
         <v>-10.64617796309836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.126914270738059</v>
+        <v>-1.027791429420298</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.618474651795417</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.560828547737782</v>
+        <v>1.659951389055544</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.231036180132794</v>
       </c>
       <c r="D1877" t="n">
         <v>-10.64248703814195</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.125437900755495</v>
+        <v>-1.026315059437734</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.618474651795417</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.560828547737782</v>
+        <v>1.659951389055544</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611694</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.236549377251436</v>
       </c>
       <c r="D1878" t="n">
         <v>-10.84674521347181</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.201627973768798</v>
+        <v>-1.102505132451037</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.746113596409406</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.489758378088031</v>
+        <v>1.588881219405793</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199884</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.241031931735872</v>
       </c>
       <c r="D1879" t="n">
         <v>-11.06478298510299</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.284360527936834</v>
+        <v>-1.185237686619072</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.920884364505305</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.389378471714928</v>
+        <v>1.48850131303269</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910626</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.256403633229294</v>
       </c>
       <c r="D1880" t="n">
         <v>-10.99131315343554</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.239600893776433</v>
+        <v>-1.140478052458671</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.847414532837857</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.448832072208818</v>
+        <v>1.54795491352658</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078593</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.27095885397681</v>
       </c>
       <c r="D1881" t="n">
         <v>-11.16643757082209</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.295095439983533</v>
+        <v>-1.195972598665771</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.0225389502244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.358312642524409</v>
+        <v>1.457435483842171</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880265</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.263739689075214</v>
       </c>
       <c r="D1882" t="n">
         <v>-11.40088966483658</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.396095442490925</v>
+        <v>-1.296972601173163</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.0225389502244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.351093477622813</v>
+        <v>1.450216318940575</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.48068891723439</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.257067498301238</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.68869350937381</v>
+        <v>-11.46856144436506</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.517889171079796</v>
+        <v>-1.330713503758534</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.310342794761639</v>
+        <v>-3.090210729752888</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.171738980126494</v>
+        <v>1.402941060449506</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.258183288139795</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.91851795653764</v>
+        <v>-11.69838589152889</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.608703160106771</v>
+        <v>-1.421527492785508</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.472990331831799</v>
+        <v>-3.252858266823048</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.075266247722954</v>
+        <v>1.306468328045966</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.260877016768909</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.1505468762739</v>
+        <v>-11.93041481126515</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.698820999372161</v>
+        <v>-1.511645332050898</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.314870964011472</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.040752358039014</v>
+        <v>1.271954438362027</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.26486735245531</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.09853136230509</v>
+        <v>-11.87839929729634</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.674024458098234</v>
+        <v>-1.486848790776972</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.314870964011472</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.044742693725415</v>
+        <v>1.275944774048428</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.263392125556568</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.24020320402921</v>
+        <v>-12.02007113902046</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.732168421686624</v>
+        <v>-1.544992754365362</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.535003029020222</v>
+        <v>-3.314870964011472</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.043267466826673</v>
+        <v>1.274469547149686</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.278445535721441</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.33910994448848</v>
+        <v>-12.11897787947973</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.756677707705462</v>
+        <v>-1.5695020403842</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.633909769479498</v>
+        <v>-3.413777704470747</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9989768327159809</v>
+        <v>1.230178913038993</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.265394402074758</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.13995783725139</v>
+        <v>-11.91982577224263</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.690067998457306</v>
+        <v>-1.502892331136044</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.468587243529684</v>
+        <v>-3.248455178520933</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.085119214639186</v>
+        <v>1.316321294962198</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.274973475110966</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.91411268453198</v>
+        <v>-11.69398061952322</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.590150864333333</v>
+        <v>-1.402975197012071</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.20652850293377</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.119854293027692</v>
+        <v>1.351056373350705</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.276112619667025</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.62783787220928</v>
+        <v>-11.40770580720053</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.474501794848196</v>
+        <v>-1.287326127526934</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.426660567942521</v>
+        <v>-3.20652850293377</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.120993437583751</v>
+        <v>1.352195517906764</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116212</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.278746393829133</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.68073316025357</v>
+        <v>-11.46060109524482</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.493026135903803</v>
+        <v>-1.30585046858254</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.201573156845324</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.126600419398927</v>
+        <v>1.357802499721939</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.284480098067769</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.39682442932482</v>
+        <v>-11.17669236431607</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.373728939293667</v>
+        <v>-1.186553271972405</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.421705221854074</v>
+        <v>-3.201573156845324</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.132334123637563</v>
+        <v>1.363536203960575</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.274742835673904</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.14983717913187</v>
+        <v>-10.92970511412311</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.284671301610351</v>
+        <v>-1.097495634289089</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.174717971661122</v>
+        <v>-2.954585906652372</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.270789211359469</v>
+        <v>1.501991291682481</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.264859354360997</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.8860003119278</v>
+        <v>-10.66586824691904</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.189020036041631</v>
+        <v>-1.001844368720369</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.174717971661122</v>
+        <v>-2.954585906652372</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.260905730046562</v>
+        <v>1.492107810369574</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.263024793861623</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.6187585110594</v>
+        <v>-10.39862644605065</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.083957876193646</v>
+        <v>-0.8967822088723838</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.174717971661122</v>
+        <v>-2.954585906652372</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.259071169547188</v>
+        <v>1.4902732498702</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.262724478888162</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.34294934765891</v>
+        <v>-10.12281728265016</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.973934525806913</v>
+        <v>-0.78675885848565</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.085698663382389</v>
+        <v>-2.865566598373638</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.312182439540967</v>
+        <v>1.54338451986398</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.263392985033656</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.31899580668296</v>
+        <v>-10.0988637416742</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.963684603271036</v>
+        <v>-0.7765089359497739</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.061745122406431</v>
+        <v>-2.841613057397681</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.327223070272036</v>
+        <v>1.558425150595047</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.250132668871903</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.05493586836016</v>
+        <v>-9.834803803351408</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8713209441036689</v>
+        <v>-0.6841452767824068</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.577553119074885</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.472398717103961</v>
+        <v>1.703600797426973</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.247345635211603</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.347856244855322</v>
+        <v>-9.12772417984657</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5912761283620354</v>
+        <v>-0.4041004610407728</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.797685184083635</v>
+        <v>-2.577553119074885</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.46961168344366</v>
+        <v>1.700813763766672</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.247689259099444</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.307671946489132</v>
+        <v>-9.08753988148038</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5748587851277178</v>
+        <v>-0.3876831178064553</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.757500885717445</v>
+        <v>-2.537368820708694</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.494065886351216</v>
+        <v>1.725267966674228</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.247056080320201</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.227602150951327</v>
+        <v>-9.007470085942575</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5434640456918389</v>
+        <v>-0.3562883783705768</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.677431090179641</v>
+        <v>-2.45729902517089</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.541474584894655</v>
+        <v>1.772676665217667</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.254980509158053</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.994120928721728</v>
+        <v>-8.773988863712976</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4421471279621469</v>
+        <v>-0.2549714606408844</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.443949867950042</v>
+        <v>-2.223817802941291</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.689487747070267</v>
+        <v>1.920689827393279</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.252088298845094</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.814412398577854</v>
+        <v>-8.594280333569102</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3731559262175566</v>
+        <v>-0.1859802588962944</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.386778363787346</v>
+        <v>-2.166646298778595</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.720898439254925</v>
+        <v>1.952100519577937</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.247455785592121</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.682136924946967</v>
+        <v>-8.462004859938215</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3248782500181746</v>
+        <v>-0.1377025826969125</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.25450289015646</v>
+        <v>-2.034370825147709</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.795631210180484</v>
+        <v>2.026833290503496</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575949</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.250270846279758</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.520261684778166</v>
+        <v>-8.300129619769415</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2573130932630177</v>
+        <v>-0.07013742594175554</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.09262764998766</v>
+        <v>-1.872495584978909</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.895571414969401</v>
+        <v>2.126773495292412</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.263177187503417</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.271261886094585</v>
+        <v>-8.051129821085834</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1448068325659264</v>
+        <v>0.0423688347553357</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.09262764998766</v>
+        <v>-1.872495584978909</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.908477756193059</v>
+        <v>2.139679836516072</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.135201257904198</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.37685187586769</v>
+        <v>-8.156719810858938</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3150187580743871</v>
+        <v>-0.1278430907531245</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.198217639760764</v>
+        <v>-1.978085574752013</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.717147832729978</v>
+        <v>1.94834991305299</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.183745599781284</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.395586777986287</v>
+        <v>-8.175454712977535</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2739683770447394</v>
+        <v>-0.0867927097234773</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.198217639760764</v>
+        <v>-1.978085574752013</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.765692174607064</v>
+        <v>1.996894254930076</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.187124611767279</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.118848603315474</v>
+        <v>-7.898716538306722</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1598940951904195</v>
+        <v>0.02728157213084259</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.016400978650839</v>
+        <v>-1.796268913642088</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.878161183259014</v>
+        <v>2.109363263582027</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.178410625513801</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.991956196880404</v>
+        <v>-7.771824131871652</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1178511188698699</v>
+        <v>0.06932454845139269</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.889508572215769</v>
+        <v>-1.669376507207018</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.945582640866578</v>
+        <v>2.17678472118959</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.171450013418708</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.948407790109713</v>
+        <v>-7.728275725100962</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1073923682566869</v>
+        <v>0.07978329906457571</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.889508572215769</v>
+        <v>-1.669376507207018</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.938622028771485</v>
+        <v>2.169824109094497</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086789526482089</v>
+        <v>3.185912367799851</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.706259396655855</v>
+        <v>-7.486127331647103</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.003929343505999494</v>
+        <v>0.1911050108272621</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.889508572215769</v>
+        <v>-1.669376507207018</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.953084383152628</v>
+        <v>2.18428646347564</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.081321646941284</v>
+        <v>3.180444488259046</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.643030024887507</v>
+        <v>-7.422897959878755</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02375321267253394</v>
+        <v>0.2109288799937965</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.889508572215769</v>
+        <v>-1.669376507207018</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.947616503611823</v>
+        <v>2.178818583934835</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262043</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.078819740951861</v>
+        <v>3.177942582269623</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.456542332510501</v>
+        <v>-7.267938354446662</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.0958463836339134</v>
+        <v>0.2704108161772103</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.703020879838762</v>
+        <v>-1.514416901774925</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.057007213048604</v>
+        <v>2.269292441204668</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389905</v>
+        <v>3.812450103389903</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.086520719189187</v>
+        <v>3.185643560506948</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.435393133607057</v>
+        <v>-7.246789155543219</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1120070414326162</v>
+        <v>0.2865714739759131</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.681871680935319</v>
+        <v>-1.493267702871482</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.077397710627995</v>
+        <v>2.289682938784059</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.082301427536237</v>
+        <v>3.181424268853999</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.191627691623613</v>
+        <v>-7.003023713559775</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2052939265730447</v>
+        <v>0.3798583591163416</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.681871680935319</v>
+        <v>-1.493267702871482</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.073178418975046</v>
+        <v>2.28546364713111</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.084425741456253</v>
+        <v>3.183548582774015</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.927599624430353</v>
+        <v>-6.738995646366515</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3130294673703644</v>
+        <v>0.4875938999136613</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.480006282119366</v>
+        <v>-1.291402304055528</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.196421972184634</v>
+        <v>2.408707200340698</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.077167816439955</v>
+        <v>3.176290657757717</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.677749230481279</v>
+        <v>-6.48914525241744</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4057116999336965</v>
+        <v>0.5802761324769934</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.480006282119366</v>
+        <v>-1.291402304055528</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.189164047168336</v>
+        <v>2.4014492753244</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080766939960604</v>
+        <v>3.179889781278366</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.3741817414773</v>
+        <v>-6.185577763413462</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5307378190559366</v>
+        <v>0.7053022515992335</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.480006282119366</v>
+        <v>-1.291402304055528</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.192763170688985</v>
+        <v>2.405048398845049</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.094094446015158</v>
+        <v>3.193217287332919</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.300701832625286</v>
+        <v>-6.112097854561448</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5734572886512961</v>
+        <v>0.748021721194593</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.406526373267351</v>
+        <v>-1.217922395203514</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.250178622054747</v>
+        <v>2.462463850210811</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.093114923631455</v>
+        <v>3.192237764949216</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.075668832956463</v>
+        <v>-5.887064854892625</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6624909661351222</v>
+        <v>0.837055398678419</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.181493373598528</v>
+        <v>-0.9928893955346912</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.384218899472338</v>
+        <v>2.596504127628402</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.097809724685772</v>
+        <v>3.196932566003534</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.861034455320056</v>
+        <v>-5.672430477256218</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7530395182440022</v>
+        <v>0.9276039507872991</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9668589959621214</v>
+        <v>-0.7782550178982844</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.517694327108499</v>
+        <v>2.729979555264563</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.079003983469568</v>
+        <v>3.178126824787329</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.594434098345705</v>
+        <v>-5.405830120281866</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8408739198175388</v>
+        <v>1.015438352360836</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9668589959621214</v>
+        <v>-0.7782550178982844</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.498888585892295</v>
+        <v>2.711173814048359</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.080747060094445</v>
+        <v>3.179869901412207</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.354003601540844</v>
+        <v>-5.165399623477006</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9387891951643601</v>
+        <v>1.113353627707657</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7264284991572612</v>
+        <v>-0.5378245210934242</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.644889960600089</v>
+        <v>2.857175188756153</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.084676373929265</v>
+        <v>3.183799215247027</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.111212793891399</v>
+        <v>-4.92260881582756</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.039834832058959</v>
+        <v>1.214399264602255</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7264284991572612</v>
+        <v>-0.5378245210934242</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.648819274434909</v>
+        <v>2.861104502590972</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.085354957846605</v>
+        <v>3.184477799164367</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.87160770228431</v>
+        <v>-4.683003724220471</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.136355452619134</v>
+        <v>1.310919885162431</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6593805514887666</v>
+        <v>-0.4707765734249296</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.689726626953346</v>
+        <v>2.902011855109409</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.082353029066599</v>
+        <v>3.18147587038436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.628952113861146</v>
+        <v>-4.440348135797308</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.230415759208393</v>
+        <v>1.40498019175169</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6593805514887666</v>
+        <v>-0.4707765734249296</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.686724698173339</v>
+        <v>2.899009926329403</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.083932066077213</v>
+        <v>3.183054907394975</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.408931315824136</v>
+        <v>-4.220327337760297</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.320003115433811</v>
+        <v>1.494567547977108</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5181607064207864</v>
+        <v>-0.3295567283569494</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.773035642224742</v>
+        <v>2.985320870380805</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.099826248879036</v>
+        <v>3.198949090196798</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.209682685919327</v>
+        <v>-4.021078707855488</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.415596750197558</v>
+        <v>1.590161182740855</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5181607064207864</v>
+        <v>-0.3295567283569494</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.788929825026565</v>
+        <v>3.001215053182628</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.100972093319338</v>
+        <v>3.2000949346371</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.050167582399957</v>
+        <v>-3.861563604336118</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.480548636045608</v>
+        <v>1.655113068588905</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3586456029014164</v>
+        <v>-0.1700416248375795</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.885784731578489</v>
+        <v>3.098069959734552</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.111060195880778</v>
+        <v>3.21018303719854</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.905495437300219</v>
+        <v>-3.716891459236381</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.548505596646943</v>
+        <v>1.72307002919024</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.213973457801679</v>
+        <v>-0.02536947973784204</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.982676121199771</v>
+        <v>3.194961349355835</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.0263998879675</v>
+        <v>3.125522729285261</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.887725978369264</v>
+        <v>-3.507154875772583</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.470953072306047</v>
+        <v>1.722304354662481</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1962039988707235</v>
+        <v>0.1843671037259554</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.908677488645066</v>
+        <v>3.236142991520835</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.471267580076584</v>
+        <v>3.466304588914411</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.958264385201043</v>
+        <v>3.147923222607827</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.887725978369264</v>
+        <v>-3.462634589047406</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.470953072306047</v>
+        <v>1.762512962675118</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1962039988707235</v>
+        <v>0.1843671037259554</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.951328182187411</v>
+        <v>3.258543484843401</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240414.xlsx
+++ b/tame_output/ON/bt/strategyON_20240414.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-6.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>119.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.4%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-700.4%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>550.1%</t>
+          <t>749.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.8%</t>
+          <t>-550.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.8%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>-128.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.0%</t>
+          <t>-226.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-317.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.6%</t>
+          <t>-251.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-174.4%</t>
+          <t>-190.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.2%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.255211538113584</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
         <v>0.2900680400748214</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.370882329829765</v>
+        <v>3.271759488512004</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.379632910658099</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43891,19 +43891,19 @@
         <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.233957919737321</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.2335984088985246</v>
+        <v>0.1274419601101828</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.327040858982983</v>
+        <v>3.185455438149885</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.711409540942887</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.324497513576058</v>
+        <v>4.161680802985292</v>
       </c>
     </row>
     <row r="1842">
@@ -43914,19 +43914,19 @@
         <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.234975528867791</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1678310188491126</v>
+        <v>0.06167457006077076</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.301751512093689</v>
+        <v>3.160166091260591</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.711409540942887</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.325515122706529</v>
+        <v>4.162698412115762</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.225603560855546</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.154295535072403</v>
+        <v>0.04813908628406116</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.28696535057076</v>
+        <v>3.145379929737663</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.711409540942887</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.316143154694284</v>
+        <v>4.153326444103517</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.215686286810785</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.07252363464465128</v>
+        <v>-0.03363281414369051</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.244339316354898</v>
+        <v>3.1027538955218</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.738445114349024</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.322447224693204</v>
+        <v>4.159630514102438</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.220451603644487</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.005314526772773609</v>
+        <v>-0.1008419220155682</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.222220990039849</v>
+        <v>3.080635569206751</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.738445114349024</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.327212541526906</v>
+        <v>4.16439583093614</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.218276399763727</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.009305979567963807</v>
+        <v>-0.09685046922037799</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.221642367277166</v>
+        <v>3.080056946444068</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.742436567144214</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.327432209323261</v>
+        <v>4.164615498732495</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.216203291268791</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4084480439788732</v>
+        <v>-0.514604492767215</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.052467649363494</v>
+        <v>2.910882228530396</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.430838992385719</v>
+        <v>1.324682543597377</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.074706686700222</v>
+        <v>3.911889976109456</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.216069507867712</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6300699775369907</v>
+        <v>-0.7362264263253324</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.963685092539169</v>
+        <v>2.822099671706071</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.393312858698349</v>
+        <v>1.287156409910008</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.052057223086722</v>
+        <v>3.889240512495956</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.220961652421638</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8380740358900679</v>
+        <v>-0.9442304846784096</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.885375613751863</v>
+        <v>2.743790192918765</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.393312858698349</v>
+        <v>1.287156409910008</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.056949367640647</v>
+        <v>3.894132657049882</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.216043108759626</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.108473998598953</v>
+        <v>-1.214630447387295</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.772297085006297</v>
+        <v>2.630711664173199</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.122912895989464</v>
+        <v>1.016756447201123</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.889790846353304</v>
+        <v>3.726974135762538</v>
       </c>
     </row>
     <row r="1851">
@@ -44121,19 +44121,19 @@
         <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.209127408066075</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.447632376187475</v>
+        <v>-1.553788824975817</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.629718033277337</v>
+        <v>2.48813261244424</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.783754518400942</v>
+        <v>0.6775980696126005</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.67938011910664</v>
+        <v>3.516563408515874</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.229465697804843</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.775649597914954</v>
+        <v>-1.881806046703296</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.518849434325114</v>
+        <v>2.377264013492016</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4557372966734629</v>
+        <v>0.3495808478851213</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.502908075808921</v>
+        <v>3.340091365218155</v>
       </c>
     </row>
     <row r="1853">
@@ -44167,19 +44167,19 @@
         <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.237564448213412</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.268974469450132</v>
+        <v>-2.375130918238474</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.329618236119612</v>
+        <v>2.188032815286514</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3507511824338441</v>
+        <v>0.2445947336455026</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.448015157673719</v>
+        <v>3.285198447082952</v>
       </c>
     </row>
     <row r="1854">
@@ -44190,19 +44190,19 @@
         <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.238670840257144</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.761359497474229</v>
+        <v>-2.867515946262571</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.133770616953705</v>
+        <v>1.992185196120607</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2477902943785941</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.153690532902993</v>
+        <v>2.990873822312226</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.237213379070008</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.146539888404301</v>
+        <v>-3.252696337192643</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.97824099939454</v>
+        <v>1.836655578561441</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1416338455902526</v>
+        <v>-0.2477902943785941</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.152233071715856</v>
+        <v>2.98941636112509</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.238982502524624</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.490222661630964</v>
+        <v>-3.596379110419306</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.842537013558491</v>
+        <v>1.700951592725392</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.3556963464058123</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.089258563954142</v>
+        <v>2.926441853363375</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.235088561180882</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.847873011869312</v>
+        <v>-3.954029460657654</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.695582932119409</v>
+        <v>1.553997511286311</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.7133466966441604</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.87077441246739</v>
+        <v>2.707957701876624</v>
       </c>
     </row>
     <row r="1858">
@@ -44282,19 +44282,19 @@
         <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.236861487881141</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.157107114865363</v>
+        <v>-4.263263563653705</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.573662217621248</v>
+        <v>1.43207679678815</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.7133466966441604</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.87254733916765</v>
+        <v>2.709730628576883</v>
       </c>
     </row>
     <row r="1859">
@@ -44305,19 +44305,19 @@
         <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.223194375348545</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.588912908015151</v>
+        <v>-4.695069356803493</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.387272787828738</v>
+        <v>1.245687366995639</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.8497641930854274</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.777029728770294</v>
+        <v>2.614213018179528</v>
       </c>
     </row>
     <row r="1860">
@@ -44328,19 +44328,19 @@
         <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.211479150350636</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.915345436882895</v>
+        <v>-5.021501885671237</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.244984551283731</v>
+        <v>1.103399130450633</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.9322324435925755</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.715833553468096</v>
+        <v>2.55301684287733</v>
       </c>
     </row>
     <row r="1861">
@@ -44351,19 +44351,19 @@
         <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.210059742006601</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.251008084113347</v>
+        <v>-5.357164532901689</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.109300084047515</v>
+        <v>0.9677146632144167</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.9322324435925755</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.714414145124061</v>
+        <v>2.551597434533295</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.216547302240843</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.61463432901366</v>
+        <v>-5.720790777802002</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9703371463216315</v>
+        <v>0.8287517254885328</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-1.030454080459701</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.661968723238027</v>
+        <v>2.499152012647261</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.215801817246674</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.979761711652407</v>
+        <v>-6.085918160440749</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8235407082719641</v>
+        <v>0.6819552874388655</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.220608415970372</v>
+        <v>-1.326764864758714</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.483436767664451</v>
+        <v>2.320620057073685</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.214563361261433</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.388350488833085</v>
+        <v>-6.494506937621427</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6588667414144518</v>
+        <v>0.5172813205813536</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.237045045370803</v>
+        <v>2.074228334780036</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.209748793732894</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.801332972974179</v>
+        <v>-6.907489421762521</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4888591802294751</v>
+        <v>0.3472737593963764</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.232230477842264</v>
+        <v>2.069413767251497</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.207742844341771</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.217724847261176</v>
+        <v>-7.323881296049518</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.3202964811235534</v>
+        <v>0.1787110602904551</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.230224528451141</v>
+        <v>2.067407817860374</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.21800153501045</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.594401857791021</v>
+        <v>-7.700558306579363</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1798843675802946</v>
+        <v>0.03829894674719636</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.24048321911982</v>
+        <v>2.077666508529053</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.214101100156145</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.940276679775829</v>
+        <v>-8.046433128564171</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0376340039320664</v>
+        <v>-0.1039514169010318</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.236582784265515</v>
+        <v>2.073766073674749</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.212506020211146</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.253101479020808</v>
+        <v>-8.35925792780915</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.08909099571092405</v>
+        <v>-0.2306764165440227</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.629197193151051</v>
+        <v>-1.735353641939392</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.234987704320516</v>
+        <v>2.07217099372975</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.216284996140355</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.549762820831006</v>
+        <v>-8.655919269619348</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2039765565057952</v>
+        <v>-0.3455619773388938</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.804096777673271</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.197520798809397</v>
+        <v>2.034704088218631</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.212258691605951</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.983111928941241</v>
+        <v>-9.089268377729583</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3813425042842926</v>
+        <v>-0.5229279251173908</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.804096777673271</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.193494494274994</v>
+        <v>2.030677783684228</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.212156590284367</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.366113317683872</v>
+        <v>-9.472269766472214</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.534645161102929</v>
+        <v>-0.6762305819360273</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.697940328884929</v>
+        <v>-1.804096777673271</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.19339239295341</v>
+        <v>2.030575682362644</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.214728106255798</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.74109864385515</v>
+        <v>-9.847255092643492</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6820677756000095</v>
+        <v>-0.8236531964331082</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.179082103844548</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.970972713222074</v>
+        <v>1.808156002631307</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.220078409553848</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.10062896635915</v>
+        <v>-10.20678541514749</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8205296013035603</v>
+        <v>-0.9621150221366586</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.072925655056207</v>
+        <v>-2.179082103844548</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.976323016520124</v>
+        <v>1.813506305929357</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.227994429511025</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.42702899502416</v>
+        <v>-10.53318544381251</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9431735928123879</v>
+        <v>-1.084759013645486</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.39932568372122</v>
+        <v>-2.505482132509561</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.788399019278294</v>
+        <v>1.625582308687527</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.231036180132794</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.64617796309836</v>
+        <v>-10.7523344118867</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.027791429420298</v>
+        <v>-1.169376850253397</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.724631100583759</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.659951389055544</v>
+        <v>1.497134678464777</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.231036180132794</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.64248703814195</v>
+        <v>-10.74864348693029</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.026315059437734</v>
+        <v>-1.167900480270832</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.618474651795417</v>
+        <v>-2.724631100583759</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.659951389055544</v>
+        <v>1.497134678464777</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.236549377251436</v>
+        <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.84674521347181</v>
+        <v>-10.95290166226016</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.102505132451037</v>
+        <v>-1.244090553284135</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.746113596409406</v>
+        <v>-2.852270045197748</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.588881219405793</v>
+        <v>1.426064508815027</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.241031931735872</v>
+        <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.06478298510299</v>
+        <v>-11.17093943389133</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.185237686619072</v>
+        <v>-1.32682310745217</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.920884364505305</v>
+        <v>-3.027040813293647</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.48850131303269</v>
+        <v>1.325684602441923</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.256403633229294</v>
+        <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.99131315343554</v>
+        <v>-11.09746960222389</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.140478052458671</v>
+        <v>-1.282063473291769</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.847414532837857</v>
+        <v>-2.953570981626198</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.54795491352658</v>
+        <v>1.385138202935813</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.27095885397681</v>
+        <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.16643757082209</v>
+        <v>-11.27259401961043</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.195972598665771</v>
+        <v>-1.33755801949887</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.128695399012742</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.457435483842171</v>
+        <v>1.294618773251404</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.263739689075214</v>
+        <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.40088966483658</v>
+        <v>-11.50704611362492</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.296972601173163</v>
+        <v>-1.438558022006262</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.0225389502244</v>
+        <v>-3.128695399012742</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.450216318940575</v>
+        <v>1.287399608349808</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.48068891723439</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.257067498301238</v>
+        <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.46856144436506</v>
+        <v>-11.79484995816216</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.330713503758534</v>
+        <v>-1.560351750595134</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.090210729752888</v>
+        <v>-3.41649924354998</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.402941060449506</v>
+        <v>1.108045110853489</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.258183288139795</v>
+        <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.69838589152889</v>
+        <v>-12.02467440532598</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.421527492785508</v>
+        <v>-1.651165739622107</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.252858266823048</v>
+        <v>-3.579146780620141</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.306468328045966</v>
+        <v>1.011572378449949</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.260877016768909</v>
+        <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.93041481126515</v>
+        <v>-12.25670332506224</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.511645332050898</v>
+        <v>-1.741283578887498</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.314870964011472</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.271954438362027</v>
+        <v>0.9770584887660094</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.26486735245531</v>
+        <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.87839929729634</v>
+        <v>-12.20468781109343</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.486848790776972</v>
+        <v>-1.716487037613572</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.314870964011472</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.275944774048428</v>
+        <v>0.9810488244524103</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.263392125556568</v>
+        <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.02007113902046</v>
+        <v>-12.34635965281755</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.544992754365362</v>
+        <v>-1.774631001201961</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.314870964011472</v>
+        <v>-3.641159477808564</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.274469547149686</v>
+        <v>0.9795735975536686</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.278445535721441</v>
+        <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.11897787947973</v>
+        <v>-12.44526639327683</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.5695020403842</v>
+        <v>-1.799140287220799</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.413777704470747</v>
+        <v>-3.740066218267839</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.230178913038993</v>
+        <v>0.9352829634429756</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.265394402074758</v>
+        <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.91982577224263</v>
+        <v>-12.24611428603973</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.502892331136044</v>
+        <v>-1.732530577972642</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.248455178520933</v>
+        <v>-3.574743692318026</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.316321294962198</v>
+        <v>1.021425345366181</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.274973475110966</v>
+        <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.69398061952322</v>
+        <v>-12.02026913332032</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.402975197012071</v>
+        <v>-1.632613443848669</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.20652850293377</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.351056373350705</v>
+        <v>1.056160423754688</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.276112619667025</v>
+        <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.40770580720053</v>
+        <v>-11.73399432099762</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.287326127526934</v>
+        <v>-1.516964374363532</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.20652850293377</v>
+        <v>-3.532817016730863</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.352195517906764</v>
+        <v>1.057299568310746</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.278746393829133</v>
+        <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.46060109524482</v>
+        <v>-11.78688960904191</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.30585046858254</v>
+        <v>-1.535488715419139</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.201573156845324</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.357802499721939</v>
+        <v>1.062906550125922</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.284480098067769</v>
+        <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.17669236431607</v>
+        <v>-11.50298087811316</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.186553271972405</v>
+        <v>-1.416191518809003</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.201573156845324</v>
+        <v>-3.527861670642416</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.363536203960575</v>
+        <v>1.068640254364558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.274742835673904</v>
+        <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.92970511412311</v>
+        <v>-11.25599362792021</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.097495634289089</v>
+        <v>-1.327133881125688</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.954585906652372</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.501991291682481</v>
+        <v>1.207095342086464</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.264859354360997</v>
+        <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.66586824691904</v>
+        <v>-10.99215676071614</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.001844368720369</v>
+        <v>-1.231482615556967</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.954585906652372</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.492107810369574</v>
+        <v>1.197211860773557</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.263024793861623</v>
+        <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.39862644605065</v>
+        <v>-10.72491495984774</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8967822088723838</v>
+        <v>-1.126420455708982</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.954585906652372</v>
+        <v>-3.280874420449464</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.4902732498702</v>
+        <v>1.195377300274183</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.262724478888162</v>
+        <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12281728265016</v>
+        <v>-10.44910579644725</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.78675885848565</v>
+        <v>-1.016397105322249</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.865566598373638</v>
+        <v>-3.191855112170731</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.54338451986398</v>
+        <v>1.248488570267962</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.263392985033656</v>
+        <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.0988637416742</v>
+        <v>-10.4251522554713</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7765089359497739</v>
+        <v>-1.006147182786372</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.841613057397681</v>
+        <v>-3.167901571194773</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.558425150595047</v>
+        <v>1.26352920099903</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.250132668871903</v>
+        <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.834803803351408</v>
+        <v>-10.1610923171485</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6841452767824068</v>
+        <v>-0.9137835236190055</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.577553119074885</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.703600797426973</v>
+        <v>1.408704847830956</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.247345635211603</v>
+        <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.12772417984657</v>
+        <v>-9.454012693643662</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4041004610407728</v>
+        <v>-0.6337387078773711</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.577553119074885</v>
+        <v>-2.903841632871977</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.700813763766672</v>
+        <v>1.405917814170655</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.247689259099444</v>
+        <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.08753988148038</v>
+        <v>-9.413828395277472</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3876831178064553</v>
+        <v>-0.6173213646430535</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.537368820708694</v>
+        <v>-2.863657334505787</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.725267966674228</v>
+        <v>1.430372017078211</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.247056080320201</v>
+        <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.007470085942575</v>
+        <v>-9.333758599739667</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3562883783705768</v>
+        <v>-0.5859266252071751</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.45729902517089</v>
+        <v>-2.783587538967982</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.772676665217667</v>
+        <v>1.47778071562165</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.254980509158053</v>
+        <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.773988863712976</v>
+        <v>-9.100277377510068</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2549714606408844</v>
+        <v>-0.4846097074774827</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.223817802941291</v>
+        <v>-2.550106316738384</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.920689827393279</v>
+        <v>1.625793877797262</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.252088298845094</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.594280333569102</v>
+        <v>-8.920568847366194</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1859802588962944</v>
+        <v>-0.4156185057328927</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.166646298778595</v>
+        <v>-2.492934812575688</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.952100519577937</v>
+        <v>1.65720456998192</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.247455785592121</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.462004859938215</v>
+        <v>-8.788293373735307</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1377025826969125</v>
+        <v>-0.3673408295335108</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.034370825147709</v>
+        <v>-2.360659338944802</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.026833290503496</v>
+        <v>1.731937340907479</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.250270846279758</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.300129619769415</v>
+        <v>-8.597693699062154</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.07013742594175554</v>
+        <v>-0.2882858989766124</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.872495584978909</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.126773495292412</v>
+        <v>1.849112206399007</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.263177187503417</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.051129821085834</v>
+        <v>-8.348693900378573</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0423688347553357</v>
+        <v>-0.1757796382795216</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.872495584978909</v>
+        <v>-2.170059664271649</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.139679836516072</v>
+        <v>1.862018547622666</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.135201257904198</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.156719810858938</v>
+        <v>-8.454283890151677</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1278430907531245</v>
+        <v>-0.3459915637879818</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.978085574752013</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.94834991305299</v>
+        <v>1.670688624159584</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.183745599781284</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.175454712977535</v>
+        <v>-8.473018792270274</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0867927097234773</v>
+        <v>-0.3049411827583342</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.978085574752013</v>
+        <v>-2.275649654044754</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.996894254930076</v>
+        <v>1.719232966036671</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.187124611767279</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.898716538306722</v>
+        <v>-8.196280617599461</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02728157213084259</v>
+        <v>-0.1908669009040147</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.796268913642088</v>
+        <v>-2.093832992934828</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.109363263582027</v>
+        <v>1.831701974688621</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.178410625513801</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.771824131871652</v>
+        <v>-8.069388211164391</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.06932454845139269</v>
+        <v>-0.1488239245834646</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.669376507207018</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.17678472118959</v>
+        <v>1.899123432296185</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.171450013418708</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.728275725100962</v>
+        <v>-8.0258398043937</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.07978329906457571</v>
+        <v>-0.1383651739702811</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.669376507207018</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.169824109094497</v>
+        <v>1.892162820201092</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.185912367799851</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.486127331647103</v>
+        <v>-7.783691410939841</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1911050108272621</v>
+        <v>-0.02704346220759479</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.669376507207018</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.18428646347564</v>
+        <v>1.906625174582235</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.180444488259046</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.422897959878755</v>
+        <v>-7.720462039171493</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2109288799937965</v>
+        <v>-0.007219593041060346</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.669376507207018</v>
+        <v>-1.966940586499758</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.178818583934835</v>
+        <v>1.90115729504143</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.177942582269623</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.267938354446662</v>
+        <v>-7.533974346794487</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2704108161772103</v>
+        <v>0.06487357792031867</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.514416901774925</v>
+        <v>-1.780452894122752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.269292441204668</v>
+        <v>2.01054800447821</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389903</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.185643560506948</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.246789155543219</v>
+        <v>-7.512825147891044</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2865714739759131</v>
+        <v>0.08103423571902191</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.493267702871482</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.289682938784059</v>
+        <v>2.030938502057602</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.181424268853999</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.003023713559775</v>
+        <v>-7.269059705907599</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3798583591163416</v>
+        <v>0.17432112085945</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.493267702871482</v>
+        <v>-1.759303695219308</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.28546364713111</v>
+        <v>2.026719210404653</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.183548582774015</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.738995646366515</v>
+        <v>-7.005031638714339</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4875938999136613</v>
+        <v>0.2820566616567701</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.291402304055528</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.408707200340698</v>
+        <v>2.149962763614241</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.176290657757717</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.48914525241744</v>
+        <v>-6.755181244765264</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5802761324769934</v>
+        <v>0.3747388942201022</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.291402304055528</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.4014492753244</v>
+        <v>2.142704838597943</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.179889781278366</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.185577763413462</v>
+        <v>-6.451613755761286</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7053022515992335</v>
+        <v>0.4997650133423424</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.291402304055528</v>
+        <v>-1.557438296403355</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.405048398845049</v>
+        <v>2.146303962118592</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.193217287332919</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.112097854561448</v>
+        <v>-6.378133846909272</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.748021721194593</v>
+        <v>0.5424844829377018</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.217922395203514</v>
+        <v>-1.48395838755134</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.462463850210811</v>
+        <v>2.203719413484354</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.192237764949216</v>
+        <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.887064854892625</v>
+        <v>-6.153100847240449</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.837055398678419</v>
+        <v>0.6315181604215279</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9928893955346912</v>
+        <v>-1.258925387882517</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.596504127628402</v>
+        <v>2.337759690901945</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.196932566003534</v>
+        <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.672430477256218</v>
+        <v>-5.938466469604042</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9276039507872991</v>
+        <v>0.7220667125304079</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7782550178982844</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.729979555264563</v>
+        <v>2.471235118538106</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.79881119554478</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.178126824787329</v>
+        <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.405830120281866</v>
+        <v>-5.67186611262969</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.015438352360836</v>
+        <v>0.8099011141039445</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7782550178982844</v>
+        <v>-1.04429101024611</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.711173814048359</v>
+        <v>2.452429377321902</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.179869901412207</v>
+        <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.165399623477006</v>
+        <v>-5.43143561582483</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.113353627707657</v>
+        <v>0.9078163894507658</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5378245210934242</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.857175188756153</v>
+        <v>2.598430752029695</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.183799215247027</v>
+        <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.92260881582756</v>
+        <v>-5.188644808175384</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.214399264602255</v>
+        <v>1.008862026345364</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5378245210934242</v>
+        <v>-0.8038605134412502</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.861104502590972</v>
+        <v>2.602360065864516</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.184477799164367</v>
+        <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.683003724220471</v>
+        <v>-4.949039716568295</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.310919885162431</v>
+        <v>1.10538264690554</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4707765734249296</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.902011855109409</v>
+        <v>2.643267418382952</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.18147587038436</v>
+        <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.440348135797308</v>
+        <v>-4.706384128145132</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.40498019175169</v>
+        <v>1.199442953494799</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4707765734249296</v>
+        <v>-0.7368125657727557</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.899009926329403</v>
+        <v>2.640265489602946</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.183054907394975</v>
+        <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.220327337760297</v>
+        <v>-4.486363330108121</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.494567547977108</v>
+        <v>1.289030309720217</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3295567283569494</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.985320870380805</v>
+        <v>2.726576433654348</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.198949090196798</v>
+        <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.021078707855488</v>
+        <v>-4.287114700203312</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.590161182740855</v>
+        <v>1.384623944483964</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3295567283569494</v>
+        <v>-0.5955927207047754</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.001215053182628</v>
+        <v>2.742470616456171</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.2000949346371</v>
+        <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.861563604336118</v>
+        <v>-4.127599596683942</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.655113068588905</v>
+        <v>1.449575830332014</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1700416248375795</v>
+        <v>-0.4360776171854055</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.098069959734552</v>
+        <v>2.839325523008095</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.21018303719854</v>
+        <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.716891459236381</v>
+        <v>-3.982927451584205</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.72307002919024</v>
+        <v>1.517532790933349</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02536947973784204</v>
+        <v>-0.2914054720856681</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.194961349355835</v>
+        <v>2.936216912629377</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.125522729285261</v>
+        <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.507154875772583</v>
+        <v>-3.965157992653249</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.722304354662481</v>
+        <v>1.439980266592453</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1843671037259554</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.236142991520835</v>
+        <v>2.862218280074672</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.466304588914411</v>
+        <v>3.535742800194638</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.147923222607827</v>
+        <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.462634589047406</v>
+        <v>-3.886882030977163</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.762512962675118</v>
+        <v>1.493691144585453</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1843671037259554</v>
+        <v>-0.2736360131547125</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.258543484843401</v>
+        <v>2.884618773397238</v>
       </c>
     </row>
   </sheetData>
